--- a/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_12_46.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_12_46.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3977208.18281102</v>
+        <v>3978286.44484618</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13582731.73276779</v>
+        <v>13593507.14668318</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13582731.73276779</v>
+        <v>13593507.14668318</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>561.0660572102443</v>
+        <v>6591.459428699664</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>561.0660572102443</v>
+        <v>6591.459428699664</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21567155.6502195</v>
+        <v>21564969.7502024</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557403</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -666,16 +666,16 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>4.889628708011855</v>
+        <v>6.843035168805314</v>
       </c>
       <c r="G2" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257416</v>
       </c>
       <c r="H2" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577661</v>
       </c>
       <c r="I2" t="n">
-        <v>1.798687867827006</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161939</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637398</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1884925285102</v>
+        <v>249.18817092047</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -742,19 +742,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>182.4392346038353</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,19 +778,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018133</v>
       </c>
       <c r="S3" t="n">
-        <v>62.48881128536601</v>
+        <v>178.361975982102</v>
       </c>
       <c r="T3" t="n">
-        <v>4.473444462796863</v>
+        <v>4.46477465147608</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886345</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>374.0000000000005</v>
       </c>
     </row>
     <row r="4">
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435316</v>
       </c>
       <c r="N4" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O4" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807365</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
-        <v>1.79868786782652</v>
+        <v>1.953406460793421</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>227.5814851567581</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,28 +1018,28 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S6" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T6" t="n">
-        <v>374</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1959257979225981</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="V6" t="n">
-        <v>14.51066719152016</v>
+        <v>128.789212606382</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="X6" t="n">
-        <v>19.86273944538755</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="Y6" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N7" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O7" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.50414770182039</v>
+        <v>87.36594612241296</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1207,22 +1207,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>192.3326389720283</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>140.4386267658497</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1255,16 +1255,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>374</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S9" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T9" t="n">
-        <v>4.473444462796863</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1276,7 +1276,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N10" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O10" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P10" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q10" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1380,13 +1380,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.36239741264436</v>
+        <v>78.40634055685446</v>
       </c>
       <c r="H11" t="n">
-        <v>72.72337227136661</v>
+        <v>72.7233722713666</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9247431442085484</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1422,7 +1422,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U11" t="n">
-        <v>328.1096985586609</v>
+        <v>328.109698558661</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
@@ -1450,22 +1450,22 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>339.6682092949317</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>3.993158516536777</v>
+        <v>3.993158516536766</v>
       </c>
       <c r="H12" t="n">
-        <v>3.95965322415698</v>
+        <v>3.959653224156966</v>
       </c>
       <c r="I12" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,22 +1492,22 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>500.932929367851</v>
+        <v>179.932929367851</v>
       </c>
       <c r="S12" t="n">
-        <v>452.7003678891396</v>
+        <v>131.7003678891396</v>
       </c>
       <c r="T12" t="n">
-        <v>81.34934068921193</v>
+        <v>81.34934068921194</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16125598660184</v>
+        <v>79.16125598660182</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>111.3731429098285</v>
+        <v>294.532409688972</v>
       </c>
       <c r="X12" t="n">
         <v>98.86273944538755</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9.517497010238188</v>
+        <v>9.517497010238174</v>
       </c>
       <c r="M13" t="n">
         <v>101.5443818943532</v>
@@ -1562,19 +1562,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O13" t="n">
-        <v>231.0003837511461</v>
+        <v>231.000383751146</v>
       </c>
       <c r="P13" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q13" t="n">
-        <v>352.442266425598</v>
+        <v>352.4422664255979</v>
       </c>
       <c r="R13" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S13" t="n">
-        <v>30.46857806351117</v>
+        <v>30.46857806351119</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1617,13 +1617,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>81.36239741264433</v>
+        <v>81.36239741264436</v>
       </c>
       <c r="H14" t="n">
-        <v>72.7233722713666</v>
+        <v>69.76731541559359</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9247431442083656</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U14" t="n">
-        <v>328.109698558661</v>
+        <v>328.1096985586609</v>
       </c>
       <c r="V14" t="n">
         <v>308.8510241668239</v>
@@ -1690,16 +1690,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>3.993158516536766</v>
+        <v>3.993158516536777</v>
       </c>
       <c r="H15" t="n">
-        <v>3.959653224156966</v>
+        <v>3.95965322415698</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1735,22 +1735,22 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T15" t="n">
-        <v>81.34934068921194</v>
+        <v>81.34934068921193</v>
       </c>
       <c r="U15" t="n">
-        <v>79.16125598660182</v>
+        <v>79.16125598660184</v>
       </c>
       <c r="V15" t="n">
-        <v>414.5106671915202</v>
+        <v>276.6699339706637</v>
       </c>
       <c r="W15" t="n">
-        <v>294.5324096889722</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>9.517497010238174</v>
+        <v>9.517497010238188</v>
       </c>
       <c r="M16" t="n">
         <v>101.5443818943532</v>
@@ -1799,19 +1799,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O16" t="n">
-        <v>231.000383751146</v>
+        <v>231.0003837511461</v>
       </c>
       <c r="P16" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q16" t="n">
-        <v>352.4422664255979</v>
+        <v>352.442266425598</v>
       </c>
       <c r="R16" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S16" t="n">
-        <v>30.46857806351119</v>
+        <v>30.46857806351117</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1854,13 +1854,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>81.36239741264436</v>
+        <v>78.40634055685446</v>
       </c>
       <c r="H17" t="n">
-        <v>72.72337227136661</v>
+        <v>72.7233722713666</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9247431442085484</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U17" t="n">
-        <v>328.1096985586609</v>
+        <v>328.109698558661</v>
       </c>
       <c r="V17" t="n">
         <v>308.8510241668239</v>
@@ -1921,25 +1921,25 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D18" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>334.4026196191416</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F18" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>324.9931585165368</v>
+        <v>3.993158516536766</v>
       </c>
       <c r="H18" t="n">
-        <v>3.95965322415698</v>
+        <v>3.959653224156966</v>
       </c>
       <c r="I18" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1972,22 +1972,22 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T18" t="n">
-        <v>81.34934068921193</v>
+        <v>81.34934068921194</v>
       </c>
       <c r="U18" t="n">
-        <v>79.16125598660184</v>
+        <v>79.16125598660182</v>
       </c>
       <c r="V18" t="n">
-        <v>93.51066719152016</v>
+        <v>276.6699339706637</v>
       </c>
       <c r="W18" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>9.517497010238188</v>
+        <v>9.517497010238174</v>
       </c>
       <c r="M19" t="n">
         <v>101.5443818943532</v>
@@ -2036,19 +2036,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O19" t="n">
-        <v>231.0003837511461</v>
+        <v>231.000383751146</v>
       </c>
       <c r="P19" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q19" t="n">
-        <v>352.442266425598</v>
+        <v>352.4422664255979</v>
       </c>
       <c r="R19" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S19" t="n">
-        <v>30.46857806351117</v>
+        <v>30.46857806351119</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2094,7 +2094,7 @@
         <v>81.36239741264433</v>
       </c>
       <c r="H20" t="n">
-        <v>72.7233722713666</v>
+        <v>69.76731541560196</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9247431442083234</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>142.0601778525742</v>
@@ -2158,16 +2158,16 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>40.09991244551929</v>
+        <v>223.2591792246629</v>
       </c>
       <c r="D21" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>3.993158516536766</v>
@@ -2215,16 +2215,16 @@
         <v>79.16125598660182</v>
       </c>
       <c r="V21" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>282.0220062245312</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y21" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="22">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>160.9993129555745</v>
+        <v>158.0432560997847</v>
       </c>
       <c r="C23" t="n">
         <v>128.4745782429939</v>
@@ -2334,7 +2334,7 @@
         <v>72.7233722713666</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9247431442083656</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2446,13 +2446,13 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T24" t="n">
-        <v>264.5086074683554</v>
+        <v>81.34934068921194</v>
       </c>
       <c r="U24" t="n">
-        <v>400.1612559866018</v>
+        <v>79.16125598660182</v>
       </c>
       <c r="V24" t="n">
-        <v>93.51066719152016</v>
+        <v>276.6699339706637</v>
       </c>
       <c r="W24" t="n">
         <v>432.3731429098285</v>
@@ -2461,7 +2461,7 @@
         <v>419.8627394453875</v>
       </c>
       <c r="Y24" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2632,25 +2632,25 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E27" t="n">
-        <v>342.6720972219126</v>
+        <v>204.8313640010562</v>
       </c>
       <c r="F27" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>3.993158516536766</v>
+        <v>324.9931585165368</v>
       </c>
       <c r="H27" t="n">
-        <v>3.959653224156966</v>
+        <v>324.959653224157</v>
       </c>
       <c r="I27" t="n">
-        <v>105.3544167830039</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>179.932929367851</v>
@@ -2695,7 +2695,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
         <v>78.39139276613435</v>
@@ -2805,7 +2805,7 @@
         <v>81.36239741264436</v>
       </c>
       <c r="H29" t="n">
-        <v>72.72337227136661</v>
+        <v>73.64811541557516</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.9247431442083234</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>142.0601778525742</v>
@@ -2866,13 +2866,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C30" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E30" t="n">
         <v>21.67209722191262</v>
@@ -2884,7 +2884,7 @@
         <v>3.993158516536777</v>
       </c>
       <c r="H30" t="n">
-        <v>324.959653224157</v>
+        <v>3.95965322415698</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2926,10 +2926,10 @@
         <v>79.16125598660184</v>
       </c>
       <c r="V30" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>294.5324096889722</v>
+        <v>294.532409688972</v>
       </c>
       <c r="X30" t="n">
         <v>419.8627394453875</v>
@@ -3039,10 +3039,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>81.36239741264433</v>
+        <v>81.36239741264436</v>
       </c>
       <c r="H32" t="n">
-        <v>73.64811541557496</v>
+        <v>72.72337227136661</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U32" t="n">
-        <v>328.109698558661</v>
+        <v>329.0344417028694</v>
       </c>
       <c r="V32" t="n">
         <v>308.8510241668239</v>
@@ -3103,25 +3103,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C33" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D33" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>21.67209722191262</v>
+        <v>204.8313640010562</v>
       </c>
       <c r="F33" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>3.993158516536766</v>
+        <v>3.993158516536777</v>
       </c>
       <c r="H33" t="n">
-        <v>3.959653224156966</v>
+        <v>3.95965322415698</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3151,22 +3151,22 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>500.932929367851</v>
+        <v>179.932929367851</v>
       </c>
       <c r="S33" t="n">
-        <v>314.859634668283</v>
+        <v>131.7003678891396</v>
       </c>
       <c r="T33" t="n">
-        <v>402.3493406892119</v>
+        <v>81.34934068921193</v>
       </c>
       <c r="U33" t="n">
-        <v>79.16125598660182</v>
+        <v>79.16125598660184</v>
       </c>
       <c r="V33" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X33" t="n">
         <v>98.86273944538755</v>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>9.517497010238174</v>
+        <v>9.517497010238188</v>
       </c>
       <c r="M34" t="n">
         <v>101.5443818943532</v>
@@ -3221,19 +3221,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O34" t="n">
-        <v>231.000383751146</v>
+        <v>231.0003837511461</v>
       </c>
       <c r="P34" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q34" t="n">
-        <v>352.4422664255979</v>
+        <v>352.442266425598</v>
       </c>
       <c r="R34" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S34" t="n">
-        <v>30.46857806351119</v>
+        <v>30.46857806351117</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3276,7 +3276,7 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>56.65754055685252</v>
+        <v>52.77674055685252</v>
       </c>
       <c r="H35" t="n">
         <v>48.7233722713666</v>
@@ -3346,7 +3346,7 @@
         <v>16.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>2.937686897702633</v>
+        <v>2.937686897702648</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3385,28 +3385,28 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>76.25280776484892</v>
       </c>
       <c r="R36" t="n">
         <v>155.932929367851</v>
       </c>
       <c r="S36" t="n">
-        <v>452.7003678891396</v>
+        <v>107.7003678891396</v>
       </c>
       <c r="T36" t="n">
         <v>57.34934068921194</v>
       </c>
       <c r="U36" t="n">
-        <v>400.1612559866018</v>
+        <v>55.16125598660182</v>
       </c>
       <c r="V36" t="n">
-        <v>69.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W36" t="n">
-        <v>87.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>306.8544131430996</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y36" t="n">
         <v>399.3913927661343</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>117.3553209967828</v>
+        <v>113.474520996848</v>
       </c>
       <c r="T38" t="n">
         <v>235.5690792160011</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>0.7758605467891769</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R39" t="n">
         <v>155.932929367851</v>
@@ -3637,16 +3637,16 @@
         <v>55.16125598660184</v>
       </c>
       <c r="V39" t="n">
-        <v>150.2589880492343</v>
+        <v>69.51066719152016</v>
       </c>
       <c r="W39" t="n">
         <v>87.37314290982852</v>
       </c>
       <c r="X39" t="n">
-        <v>419.8627394453875</v>
+        <v>74.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>54.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="40">
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>136.2944560997828</v>
+        <v>136.9993129555745</v>
       </c>
       <c r="C41" t="n">
         <v>104.4745782429939</v>
@@ -3750,10 +3750,10 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>57.36239741264433</v>
+        <v>57.36239741264435</v>
       </c>
       <c r="H41" t="n">
-        <v>48.7233722713666</v>
+        <v>48.72337227136661</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,13 +3786,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>118.0601778525742</v>
+        <v>113.4745209967827</v>
       </c>
       <c r="T41" t="n">
         <v>235.5690792160011</v>
       </c>
       <c r="U41" t="n">
-        <v>304.109698558661</v>
+        <v>304.1096985586609</v>
       </c>
       <c r="V41" t="n">
         <v>284.8510241668239</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>39.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C42" t="n">
         <v>16.09991244551929</v>
@@ -3823,19 +3823,19 @@
         <v>2.937686897702633</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>324.9931585165368</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R42" t="n">
         <v>500.932929367851</v>
@@ -3868,13 +3868,13 @@
         <v>107.7003678891396</v>
       </c>
       <c r="T42" t="n">
-        <v>57.34934068921194</v>
+        <v>402.3493406892119</v>
       </c>
       <c r="U42" t="n">
-        <v>161.2801759899022</v>
+        <v>55.16125598660184</v>
       </c>
       <c r="V42" t="n">
-        <v>69.51066719152016</v>
+        <v>221.5298805783149</v>
       </c>
       <c r="W42" t="n">
         <v>87.37314290982852</v>
@@ -3926,25 +3926,25 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>77.54438189435319</v>
+        <v>77.54438189435318</v>
       </c>
       <c r="N43" t="n">
         <v>130.4301408454554</v>
       </c>
       <c r="O43" t="n">
-        <v>207.000383751146</v>
+        <v>207.0003837511461</v>
       </c>
       <c r="P43" t="n">
         <v>266.7677661807365</v>
       </c>
       <c r="Q43" t="n">
-        <v>328.4422664255979</v>
+        <v>328.442266425598</v>
       </c>
       <c r="R43" t="n">
         <v>353.4666853582003</v>
       </c>
       <c r="S43" t="n">
-        <v>6.468578063511188</v>
+        <v>6.468578063511176</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>136.2944560997828</v>
+        <v>136.9993129555745</v>
       </c>
       <c r="C44" t="n">
         <v>104.4745782429939</v>
@@ -3987,7 +3987,7 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>57.36239741264435</v>
+        <v>52.7767405568525</v>
       </c>
       <c r="H44" t="n">
         <v>48.72337227136661</v>
@@ -4060,19 +4060,19 @@
         <v>2.937686897702633</v>
       </c>
       <c r="E45" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>324.9931585165368</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,10 +4096,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R45" t="n">
-        <v>155.932929367851</v>
+        <v>500.932929367851</v>
       </c>
       <c r="S45" t="n">
         <v>452.7003678891396</v>
@@ -4114,13 +4114,13 @@
         <v>69.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>87.37314290982852</v>
+        <v>239.3923562966233</v>
       </c>
       <c r="X45" t="n">
         <v>74.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>155.1465551073116</v>
+        <v>54.39139276613435</v>
       </c>
     </row>
     <row r="46">
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.7310038072325</v>
+        <v>108.8416377852049</v>
       </c>
       <c r="C2" t="n">
-        <v>58.75668234966289</v>
+        <v>58.86731632763525</v>
       </c>
       <c r="D2" t="n">
-        <v>48.31309069324896</v>
+        <v>48.42372467122129</v>
       </c>
       <c r="E2" t="n">
-        <v>43.9057274539877</v>
+        <v>44.01636143196004</v>
       </c>
       <c r="F2" t="n">
-        <v>38.96670855700603</v>
+        <v>37.10420469579305</v>
       </c>
       <c r="G2" t="n">
-        <v>35.58557518755156</v>
+        <v>33.72713203391687</v>
       </c>
       <c r="H2" t="n">
-        <v>31.73685643214849</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="I2" t="n">
-        <v>29.92</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>30.01969029977268</v>
       </c>
       <c r="K2" t="n">
-        <v>400.18</v>
+        <v>82.164278792235</v>
       </c>
       <c r="L2" t="n">
-        <v>464.2419149748744</v>
+        <v>326.5557936111294</v>
       </c>
       <c r="M2" t="n">
-        <v>464.2419149748744</v>
+        <v>696.8157936111299</v>
       </c>
       <c r="N2" t="n">
-        <v>464.2419149748744</v>
+        <v>1067.07579361113</v>
       </c>
       <c r="O2" t="n">
-        <v>755.48</v>
+        <v>1067.07579361113</v>
       </c>
       <c r="P2" t="n">
-        <v>1125.74</v>
+        <v>1125.740000000002</v>
       </c>
       <c r="Q2" t="n">
-        <v>1496</v>
+        <v>1496.000000000002</v>
       </c>
       <c r="R2" t="n">
-        <v>1496</v>
+        <v>1496.000000000002</v>
       </c>
       <c r="S2" t="n">
-        <v>1409.632174038565</v>
+        <v>1409.724707412508</v>
       </c>
       <c r="T2" t="n">
-        <v>1222.884106610596</v>
+        <v>1222.994415731963</v>
       </c>
       <c r="U2" t="n">
-        <v>971.1785586019998</v>
+        <v>971.2891925799727</v>
       </c>
       <c r="V2" t="n">
-        <v>739.0058069183393</v>
+        <v>739.1164408963122</v>
       </c>
       <c r="W2" t="n">
-        <v>498.2245180486953</v>
+        <v>498.3351520266681</v>
       </c>
       <c r="X2" t="n">
-        <v>304.0004438460006</v>
+        <v>304.1110778239735</v>
       </c>
       <c r="Y2" t="n">
-        <v>191.5585926512467</v>
+        <v>191.6692266292195</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1225.740689833893</v>
+        <v>584.60161418237</v>
       </c>
       <c r="C3" t="n">
-        <v>1225.740689833893</v>
+        <v>584.60161418237</v>
       </c>
       <c r="D3" t="n">
-        <v>1225.740689833893</v>
+        <v>584.60161418237</v>
       </c>
       <c r="E3" t="n">
-        <v>879.6072582966071</v>
+        <v>584.60161418237</v>
       </c>
       <c r="F3" t="n">
-        <v>695.3252031412179</v>
+        <v>241.534702729969</v>
       </c>
       <c r="G3" t="n">
-        <v>366.5169812739328</v>
+        <v>241.534702729969</v>
       </c>
       <c r="H3" t="n">
-        <v>33.13396963146437</v>
+        <v>241.534702729969</v>
       </c>
       <c r="I3" t="n">
-        <v>33.13396963146437</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="J3" t="n">
-        <v>177.6113405614803</v>
+        <v>174.5985557413368</v>
       </c>
       <c r="K3" t="n">
-        <v>401.8775591086939</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L3" t="n">
-        <v>720.3885386284223</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M3" t="n">
-        <v>861.5031803712816</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N3" t="n">
-        <v>1051.274153846774</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.994549492757</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P3" t="n">
-        <v>1496</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1496</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R3" t="n">
-        <v>1360.997993968056</v>
+        <v>1214.671396474091</v>
       </c>
       <c r="S3" t="n">
-        <v>1297.877982568697</v>
+        <v>1034.507784370957</v>
       </c>
       <c r="T3" t="n">
-        <v>1293.359351798195</v>
+        <v>1029.997910985628</v>
       </c>
       <c r="U3" t="n">
-        <v>1293.161446951808</v>
+        <v>1029.800149078064</v>
       </c>
       <c r="V3" t="n">
-        <v>1278.504207364414</v>
+        <v>1015.14290949067</v>
       </c>
       <c r="W3" t="n">
-        <v>1245.804063011052</v>
+        <v>982.4427651373074</v>
       </c>
       <c r="X3" t="n">
-        <v>1225.740689833893</v>
+        <v>962.3793919601483</v>
       </c>
       <c r="Y3" t="n">
-        <v>1225.740689833893</v>
+        <v>584.60161418237</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>182.101013416203</v>
+        <v>652.7906108062774</v>
       </c>
       <c r="C4" t="n">
-        <v>308.1030192346387</v>
+        <v>652.7906108062774</v>
       </c>
       <c r="D4" t="n">
-        <v>308.1030192346387</v>
+        <v>652.7906108062774</v>
       </c>
       <c r="E4" t="n">
-        <v>425.9319234460518</v>
+        <v>652.7906108062774</v>
       </c>
       <c r="F4" t="n">
-        <v>550.2928960379872</v>
+        <v>652.7906108062774</v>
       </c>
       <c r="G4" t="n">
-        <v>654.5935815663379</v>
+        <v>652.7906108062774</v>
       </c>
       <c r="H4" t="n">
-        <v>654.5935815663379</v>
+        <v>652.7906108062774</v>
       </c>
       <c r="I4" t="n">
-        <v>881.2025562401257</v>
+        <v>879.45327269318</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.462556240126</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K4" t="n">
-        <v>1382.983127881912</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L4" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M4" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N4" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O4" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P4" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R4" t="n">
-        <v>29.92</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="S4" t="n">
-        <v>70.34367574991084</v>
+        <v>70.37478771712398</v>
       </c>
       <c r="T4" t="n">
-        <v>70.34367574991084</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="U4" t="n">
-        <v>70.34367574991084</v>
+        <v>505.7973598420843</v>
       </c>
       <c r="V4" t="n">
-        <v>70.34367574991084</v>
+        <v>652.7906108062774</v>
       </c>
       <c r="W4" t="n">
-        <v>70.34367574991084</v>
+        <v>652.7906108062774</v>
       </c>
       <c r="X4" t="n">
-        <v>70.34367574991084</v>
+        <v>652.7906108062774</v>
       </c>
       <c r="Y4" t="n">
-        <v>70.34367574991084</v>
+        <v>652.7906108062774</v>
       </c>
     </row>
     <row r="5">
@@ -4534,76 +4534,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.731003807232</v>
+        <v>108.8416377852049</v>
       </c>
       <c r="C5" t="n">
-        <v>58.7566823496624</v>
+        <v>58.86731632763524</v>
       </c>
       <c r="D5" t="n">
-        <v>48.31309069324847</v>
+        <v>48.42372467122131</v>
       </c>
       <c r="E5" t="n">
-        <v>43.90572745398721</v>
+        <v>44.01636143196005</v>
       </c>
       <c r="F5" t="n">
-        <v>38.96670855700554</v>
+        <v>39.07734253497838</v>
       </c>
       <c r="G5" t="n">
-        <v>35.58557518755106</v>
+        <v>35.70026987310217</v>
       </c>
       <c r="H5" t="n">
-        <v>31.736856432148</v>
+        <v>31.89313783918531</v>
       </c>
       <c r="I5" t="n">
-        <v>29.92</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="J5" t="n">
-        <v>400.18</v>
+        <v>30.01969029977268</v>
       </c>
       <c r="K5" t="n">
-        <v>770.4399999999999</v>
+        <v>82.164278792235</v>
       </c>
       <c r="L5" t="n">
-        <v>834.5019149748742</v>
+        <v>326.5557936111294</v>
       </c>
       <c r="M5" t="n">
-        <v>834.5019149748744</v>
+        <v>696.8157936111299</v>
       </c>
       <c r="N5" t="n">
-        <v>1067.648108133742</v>
+        <v>1067.07579361113</v>
       </c>
       <c r="O5" t="n">
-        <v>1067.648108133742</v>
+        <v>1067.07579361113</v>
       </c>
       <c r="P5" t="n">
-        <v>1125.74</v>
+        <v>1125.740000000002</v>
       </c>
       <c r="Q5" t="n">
-        <v>1496</v>
+        <v>1496.000000000002</v>
       </c>
       <c r="R5" t="n">
-        <v>1496</v>
+        <v>1496.000000000002</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.632174038565</v>
+        <v>1409.724707412508</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.884106610596</v>
+        <v>1222.994415731963</v>
       </c>
       <c r="U5" t="n">
-        <v>971.1785586019998</v>
+        <v>971.2891925799727</v>
       </c>
       <c r="V5" t="n">
-        <v>739.0058069183393</v>
+        <v>739.1164408963122</v>
       </c>
       <c r="W5" t="n">
-        <v>498.2245180486953</v>
+        <v>498.3351520266681</v>
       </c>
       <c r="X5" t="n">
-        <v>304.0004438460006</v>
+        <v>304.1110778239735</v>
       </c>
       <c r="Y5" t="n">
-        <v>191.5585926512467</v>
+        <v>191.6692266292195</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>471.4897954173747</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="C6" t="n">
-        <v>471.4897954173747</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="D6" t="n">
-        <v>241.6095073802453</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="E6" t="n">
-        <v>241.6095073802453</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="F6" t="n">
-        <v>241.6095073802453</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="G6" t="n">
-        <v>241.6095073802453</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="H6" t="n">
-        <v>241.6095073802453</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="I6" t="n">
-        <v>29.92</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="J6" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413368</v>
       </c>
       <c r="K6" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L6" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M6" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N6" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P6" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1357.784024336592</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S6" t="n">
-        <v>1294.664012937232</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T6" t="n">
-        <v>916.8862351594544</v>
+        <v>1293.343447077155</v>
       </c>
       <c r="U6" t="n">
-        <v>916.6883303130679</v>
+        <v>915.5656692993769</v>
       </c>
       <c r="V6" t="n">
-        <v>902.0310907256738</v>
+        <v>785.4755555555566</v>
       </c>
       <c r="W6" t="n">
-        <v>869.3309463723117</v>
+        <v>407.6977777777784</v>
       </c>
       <c r="X6" t="n">
-        <v>849.2675731951525</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="Y6" t="n">
-        <v>471.4897954173747</v>
+        <v>29.92000000000004</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>871.2649205974853</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="C7" t="n">
-        <v>871.2649205974853</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="D7" t="n">
-        <v>871.2649205974853</v>
+        <v>85.85883935008873</v>
       </c>
       <c r="E7" t="n">
-        <v>871.2649205974853</v>
+        <v>203.6877435615017</v>
       </c>
       <c r="F7" t="n">
-        <v>871.2649205974853</v>
+        <v>328.0487161534372</v>
       </c>
       <c r="G7" t="n">
-        <v>1024.853581566338</v>
+        <v>481.6391623681914</v>
       </c>
       <c r="H7" t="n">
-        <v>1024.853581566338</v>
+        <v>652.7906108062774</v>
       </c>
       <c r="I7" t="n">
-        <v>1251.462556240126</v>
+        <v>879.45327269318</v>
       </c>
       <c r="J7" t="n">
-        <v>1251.462556240126</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K7" t="n">
-        <v>1382.983127881912</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M7" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N7" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O7" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P7" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R7" t="n">
-        <v>29.92</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="S7" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="T7" t="n">
-        <v>253.991484354559</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="U7" t="n">
-        <v>500.552609451862</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="V7" t="n">
-        <v>699.374002337808</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="W7" t="n">
-        <v>871.2649205974853</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="X7" t="n">
-        <v>871.2649205974853</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="Y7" t="n">
-        <v>871.2649205974853</v>
+        <v>29.92000000000004</v>
       </c>
     </row>
     <row r="8">
@@ -4771,76 +4771,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.731003807232</v>
+        <v>106.8684999460196</v>
       </c>
       <c r="C8" t="n">
-        <v>58.7566823496624</v>
+        <v>56.89417848844996</v>
       </c>
       <c r="D8" t="n">
-        <v>48.31309069324847</v>
+        <v>46.45058683203603</v>
       </c>
       <c r="E8" t="n">
-        <v>43.90572745398721</v>
+        <v>42.04322359277477</v>
       </c>
       <c r="F8" t="n">
-        <v>38.96670855700554</v>
+        <v>37.1042046957931</v>
       </c>
       <c r="G8" t="n">
-        <v>35.58557518755106</v>
+        <v>33.7271320339169</v>
       </c>
       <c r="H8" t="n">
-        <v>31.736856432148</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="I8" t="n">
-        <v>29.92</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="J8" t="n">
-        <v>275.4897777819832</v>
+        <v>400.1800000000005</v>
       </c>
       <c r="K8" t="n">
-        <v>327.128108133742</v>
+        <v>452.3245884924629</v>
       </c>
       <c r="L8" t="n">
-        <v>697.388108133742</v>
+        <v>517.014561457287</v>
       </c>
       <c r="M8" t="n">
-        <v>1067.648108133742</v>
+        <v>696.8157936111299</v>
       </c>
       <c r="N8" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.07579361113</v>
       </c>
       <c r="O8" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.07579361113</v>
       </c>
       <c r="P8" t="n">
-        <v>1496</v>
+        <v>1125.740000000002</v>
       </c>
       <c r="Q8" t="n">
-        <v>1496</v>
+        <v>1496.000000000002</v>
       </c>
       <c r="R8" t="n">
-        <v>1496</v>
+        <v>1496.000000000002</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U8" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V8" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W8" t="n">
-        <v>498.2245180486953</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X8" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.5585926512467</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="9">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>224.1953929010388</v>
+        <v>1225.724928051676</v>
       </c>
       <c r="C9" t="n">
-        <v>224.1953929010388</v>
+        <v>860.9775417430701</v>
       </c>
       <c r="D9" t="n">
-        <v>224.1953929010388</v>
+        <v>860.9775417430701</v>
       </c>
       <c r="E9" t="n">
-        <v>29.92</v>
+        <v>514.8441102057845</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92</v>
+        <v>171.7771987533836</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="H9" t="n">
-        <v>29.92</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="I9" t="n">
-        <v>29.92</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="J9" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413368</v>
       </c>
       <c r="K9" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L9" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M9" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N9" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P9" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1115.008252590758</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S9" t="n">
-        <v>1051.888241191398</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T9" t="n">
-        <v>1047.369610420896</v>
+        <v>1293.343447077155</v>
       </c>
       <c r="U9" t="n">
-        <v>1047.17170557451</v>
+        <v>1293.145685169591</v>
       </c>
       <c r="V9" t="n">
-        <v>1032.514465987116</v>
+        <v>1278.488445582197</v>
       </c>
       <c r="W9" t="n">
-        <v>999.8143216337536</v>
+        <v>1245.788301228835</v>
       </c>
       <c r="X9" t="n">
-        <v>979.7509484565944</v>
+        <v>1225.724928051676</v>
       </c>
       <c r="Y9" t="n">
-        <v>601.9731706788166</v>
+        <v>1225.724928051676</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>691.1022302167319</v>
+        <v>989.6867723914826</v>
       </c>
       <c r="C10" t="n">
-        <v>817.1042360351677</v>
+        <v>989.6867723914826</v>
       </c>
       <c r="D10" t="n">
-        <v>930.4233801601678</v>
+        <v>989.6867723914826</v>
       </c>
       <c r="E10" t="n">
-        <v>1048.252284371581</v>
+        <v>1107.515676602896</v>
       </c>
       <c r="F10" t="n">
-        <v>1048.252284371581</v>
+        <v>1231.876649194831</v>
       </c>
       <c r="G10" t="n">
-        <v>1201.840945340433</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="H10" t="n">
-        <v>1201.840945340433</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="I10" t="n">
-        <v>1251.462556240126</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="J10" t="n">
-        <v>1251.462556240126</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="K10" t="n">
-        <v>1382.983127881912</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L10" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M10" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N10" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O10" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P10" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R10" t="n">
-        <v>29.92</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="S10" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="T10" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92000000000004</v>
       </c>
       <c r="U10" t="n">
-        <v>316.9048008472139</v>
+        <v>276.4812224743523</v>
       </c>
       <c r="V10" t="n">
-        <v>316.9048008472139</v>
+        <v>443.5984247622873</v>
       </c>
       <c r="W10" t="n">
-        <v>316.9048008472139</v>
+        <v>615.4893430219647</v>
       </c>
       <c r="X10" t="n">
-        <v>467.9355918714074</v>
+        <v>766.5201340461582</v>
       </c>
       <c r="Y10" t="n">
-        <v>579.3448925504397</v>
+        <v>877.9294347251905</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>597.4524900262059</v>
+        <v>593.4524900262074</v>
       </c>
       <c r="C11" t="n">
-        <v>467.6801887706564</v>
+        <v>463.680188770658</v>
       </c>
       <c r="D11" t="n">
-        <v>377.4386173162627</v>
+        <v>373.4386173162642</v>
       </c>
       <c r="E11" t="n">
-        <v>293.2332742790216</v>
+        <v>289.2332742790232</v>
       </c>
       <c r="F11" t="n">
-        <v>208.4962755840601</v>
+        <v>204.4962755840617</v>
       </c>
       <c r="G11" t="n">
-        <v>126.3120357733083</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H11" t="n">
-        <v>52.85408398404904</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I11" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J11" t="n">
-        <v>560.4418942939371</v>
+        <v>560.3618942939372</v>
       </c>
       <c r="K11" t="n">
-        <v>786.3688492358079</v>
+        <v>736.0334691180578</v>
       </c>
       <c r="L11" t="n">
-        <v>1004.304971748371</v>
+        <v>953.9695916306206</v>
       </c>
       <c r="M11" t="n">
-        <v>1646.814971748371</v>
+        <v>1001.294971748371</v>
       </c>
       <c r="N11" t="n">
-        <v>1646.814971748371</v>
+        <v>1642.814971748373</v>
       </c>
       <c r="O11" t="n">
-        <v>1809.956778005698</v>
+        <v>1805.9567780057</v>
       </c>
       <c r="P11" t="n">
-        <v>2008.265727912157</v>
+        <v>2004.265727912159</v>
       </c>
       <c r="Q11" t="n">
-        <v>2596</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="R11" t="n">
-        <v>2596</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="S11" t="n">
-        <v>2452.504870855986</v>
+        <v>2448.504870855988</v>
       </c>
       <c r="T11" t="n">
-        <v>2190.313881748914</v>
+        <v>2186.313881748916</v>
       </c>
       <c r="U11" t="n">
-        <v>1858.889943810873</v>
+        <v>1854.889943810874</v>
       </c>
       <c r="V11" t="n">
-        <v>1546.919212329232</v>
+        <v>1542.919212329234</v>
       </c>
       <c r="W11" t="n">
-        <v>1226.339943661608</v>
+        <v>1222.33994366161</v>
       </c>
       <c r="X11" t="n">
-        <v>952.317889660934</v>
+        <v>948.3178896609356</v>
       </c>
       <c r="Y11" t="n">
-        <v>760.0780586682004</v>
+        <v>756.0780586682019</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>677.6351691139887</v>
+        <v>1141.030657215864</v>
       </c>
       <c r="C12" t="n">
-        <v>637.1302070478076</v>
+        <v>1100.525695149683</v>
       </c>
       <c r="D12" t="n">
-        <v>294.0310057397958</v>
+        <v>749.0734861621044</v>
       </c>
       <c r="E12" t="n">
-        <v>272.1399984449345</v>
+        <v>402.9400546248189</v>
       </c>
       <c r="F12" t="n">
-        <v>253.3155112349579</v>
+        <v>59.87314317241795</v>
       </c>
       <c r="G12" t="n">
-        <v>249.2820177839106</v>
+        <v>55.83964972137071</v>
       </c>
       <c r="H12" t="n">
-        <v>245.2823680625399</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I12" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J12" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K12" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L12" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M12" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N12" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O12" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P12" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R12" t="n">
-        <v>1747.236647421212</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S12" t="n">
-        <v>1289.963548543293</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T12" t="n">
-        <v>1207.792497342069</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U12" t="n">
-        <v>1127.831632709137</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V12" t="n">
-        <v>1033.376413323763</v>
+        <v>1681.781261808612</v>
       </c>
       <c r="W12" t="n">
-        <v>920.8782891724215</v>
+        <v>1384.273777274297</v>
       </c>
       <c r="X12" t="n">
-        <v>821.0169361972826</v>
+        <v>1284.412424299158</v>
       </c>
       <c r="Y12" t="n">
-        <v>741.8337111809852</v>
+        <v>1205.229199282861</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>686.6672726401017</v>
+        <v>681.4588756890412</v>
       </c>
       <c r="C13" t="n">
-        <v>734.4592784585375</v>
+        <v>729.2508815074769</v>
       </c>
       <c r="D13" t="n">
-        <v>769.5684225835375</v>
+        <v>764.360025632477</v>
       </c>
       <c r="E13" t="n">
-        <v>809.1873267949505</v>
+        <v>803.97892984389</v>
       </c>
       <c r="F13" t="n">
-        <v>855.338299386886</v>
+        <v>850.1299024358254</v>
       </c>
       <c r="G13" t="n">
-        <v>931.1543456016401</v>
+        <v>925.9459486505796</v>
       </c>
       <c r="H13" t="n">
-        <v>1027.968674039726</v>
+        <v>1022.760277088666</v>
       </c>
       <c r="I13" t="n">
-        <v>1189.521015926629</v>
+        <v>1184.312618975568</v>
       </c>
       <c r="J13" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K13" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L13" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M13" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N13" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O13" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P13" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568783</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380925</v>
       </c>
       <c r="R13" t="n">
-        <v>82.69634147829412</v>
+        <v>82.61634147829417</v>
       </c>
       <c r="S13" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="T13" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506082</v>
       </c>
       <c r="U13" t="n">
-        <v>332.8075321249603</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V13" t="n">
-        <v>453.4189250109063</v>
+        <v>448.2105280598458</v>
       </c>
       <c r="W13" t="n">
-        <v>547.0998432705837</v>
+        <v>541.8914463195232</v>
       </c>
       <c r="X13" t="n">
-        <v>619.9206342947773</v>
+        <v>614.7122373437168</v>
       </c>
       <c r="Y13" t="n">
-        <v>653.1199349738096</v>
+        <v>647.911538022749</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>597.4524900262056</v>
+        <v>593.4524900262245</v>
       </c>
       <c r="C14" t="n">
-        <v>467.6801887706562</v>
+        <v>463.680188770675</v>
       </c>
       <c r="D14" t="n">
-        <v>377.4386173162624</v>
+        <v>373.4386173162813</v>
       </c>
       <c r="E14" t="n">
-        <v>293.2332742790214</v>
+        <v>289.2332742790402</v>
       </c>
       <c r="F14" t="n">
-        <v>208.4962755840599</v>
+        <v>204.4962755840788</v>
       </c>
       <c r="G14" t="n">
-        <v>126.3120357733081</v>
+        <v>122.3120357733269</v>
       </c>
       <c r="H14" t="n">
-        <v>52.85408398404886</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I14" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J14" t="n">
-        <v>555.9215464995305</v>
+        <v>560.3618942939372</v>
       </c>
       <c r="K14" t="n">
-        <v>731.5931213236511</v>
+        <v>736.0334691180578</v>
       </c>
       <c r="L14" t="n">
-        <v>949.5292438362139</v>
+        <v>953.9695916306206</v>
       </c>
       <c r="M14" t="n">
-        <v>1592.039243836214</v>
+        <v>1589.029243836213</v>
       </c>
       <c r="N14" t="n">
-        <v>2234.549243836214</v>
+        <v>2230.549243836216</v>
       </c>
       <c r="O14" t="n">
-        <v>2397.691050093541</v>
+        <v>2393.691050093543</v>
       </c>
       <c r="P14" t="n">
-        <v>2596</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="Q14" t="n">
-        <v>2596</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="R14" t="n">
-        <v>2596</v>
+        <v>2592.000000000019</v>
       </c>
       <c r="S14" t="n">
-        <v>2452.504870855986</v>
+        <v>2448.504870856004</v>
       </c>
       <c r="T14" t="n">
-        <v>2190.313881748914</v>
+        <v>2186.313881748933</v>
       </c>
       <c r="U14" t="n">
-        <v>1858.889943810872</v>
+        <v>1854.889943810891</v>
       </c>
       <c r="V14" t="n">
-        <v>1546.919212329232</v>
+        <v>1542.919212329251</v>
       </c>
       <c r="W14" t="n">
-        <v>1226.339943661608</v>
+        <v>1222.339943661627</v>
       </c>
       <c r="X14" t="n">
-        <v>952.3178896609338</v>
+        <v>948.3178896609527</v>
       </c>
       <c r="Y14" t="n">
-        <v>760.0780586682001</v>
+        <v>756.078058668219</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>816.8682329734396</v>
+        <v>168.3033844885911</v>
       </c>
       <c r="C15" t="n">
-        <v>776.3632709072585</v>
+        <v>127.79842242241</v>
       </c>
       <c r="D15" t="n">
-        <v>749.1534861621044</v>
+        <v>100.5886376772558</v>
       </c>
       <c r="E15" t="n">
-        <v>403.0200546248188</v>
+        <v>78.69763038239461</v>
       </c>
       <c r="F15" t="n">
-        <v>59.95314317241791</v>
+        <v>59.87314317241798</v>
       </c>
       <c r="G15" t="n">
-        <v>55.91964972137067</v>
+        <v>55.83964972137073</v>
       </c>
       <c r="H15" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I15" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J15" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K15" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L15" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M15" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N15" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O15" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P15" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R15" t="n">
-        <v>2071.479071663636</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S15" t="n">
-        <v>1938.448397028141</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T15" t="n">
-        <v>1856.277345826917</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U15" t="n">
-        <v>1776.316481193986</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V15" t="n">
-        <v>1357.618837566188</v>
+        <v>1496.771901425639</v>
       </c>
       <c r="W15" t="n">
-        <v>1060.111353031872</v>
+        <v>1060.031353031873</v>
       </c>
       <c r="X15" t="n">
-        <v>960.2500000567335</v>
+        <v>635.9275758143093</v>
       </c>
       <c r="Y15" t="n">
-        <v>881.0667750404361</v>
+        <v>232.5019265555877</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>681.5388756890411</v>
+        <v>686.5872726401018</v>
       </c>
       <c r="C16" t="n">
-        <v>729.3308815074769</v>
+        <v>734.3792784585376</v>
       </c>
       <c r="D16" t="n">
-        <v>764.4400256324769</v>
+        <v>769.4884225835376</v>
       </c>
       <c r="E16" t="n">
-        <v>804.0589298438899</v>
+        <v>809.1073267949506</v>
       </c>
       <c r="F16" t="n">
-        <v>850.2099024358254</v>
+        <v>850.1299024358254</v>
       </c>
       <c r="G16" t="n">
-        <v>926.0259486505795</v>
+        <v>925.9459486505796</v>
       </c>
       <c r="H16" t="n">
-        <v>1022.840277088666</v>
+        <v>1022.760277088666</v>
       </c>
       <c r="I16" t="n">
-        <v>1184.392618975568</v>
+        <v>1184.312618975568</v>
       </c>
       <c r="J16" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K16" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L16" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M16" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N16" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O16" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P16" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568783</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380924</v>
       </c>
       <c r="R16" t="n">
-        <v>82.69634147829413</v>
+        <v>82.61634147829416</v>
       </c>
       <c r="S16" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="T16" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506082</v>
       </c>
       <c r="U16" t="n">
-        <v>332.8075321249603</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V16" t="n">
-        <v>453.4189250109063</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W16" t="n">
-        <v>541.9714463195231</v>
+        <v>547.0198432705838</v>
       </c>
       <c r="X16" t="n">
-        <v>614.7922373437167</v>
+        <v>619.8406342947774</v>
       </c>
       <c r="Y16" t="n">
-        <v>647.991538022749</v>
+        <v>653.0399349738096</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>597.4524900262059</v>
+        <v>593.4524900262074</v>
       </c>
       <c r="C17" t="n">
-        <v>467.6801887706564</v>
+        <v>463.680188770658</v>
       </c>
       <c r="D17" t="n">
-        <v>377.4386173162627</v>
+        <v>373.4386173162642</v>
       </c>
       <c r="E17" t="n">
-        <v>293.2332742790216</v>
+        <v>289.2332742790232</v>
       </c>
       <c r="F17" t="n">
-        <v>208.4962755840601</v>
+        <v>204.4962755840617</v>
       </c>
       <c r="G17" t="n">
-        <v>126.3120357733083</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H17" t="n">
-        <v>52.85408398404904</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I17" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J17" t="n">
-        <v>134.440205073642</v>
+        <v>560.3618942939372</v>
       </c>
       <c r="K17" t="n">
-        <v>470.1610500935411</v>
+        <v>1201.881894293938</v>
       </c>
       <c r="L17" t="n">
-        <v>1112.671050093541</v>
+        <v>1419.818016806501</v>
       </c>
       <c r="M17" t="n">
-        <v>1112.671050093541</v>
+        <v>2061.338016806501</v>
       </c>
       <c r="N17" t="n">
-        <v>1755.181050093541</v>
+        <v>2230.549243836216</v>
       </c>
       <c r="O17" t="n">
-        <v>2397.691050093541</v>
+        <v>2393.691050093543</v>
       </c>
       <c r="P17" t="n">
-        <v>2596</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="Q17" t="n">
-        <v>2596</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="R17" t="n">
-        <v>2596</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="S17" t="n">
-        <v>2452.504870855986</v>
+        <v>2448.504870855988</v>
       </c>
       <c r="T17" t="n">
-        <v>2190.313881748914</v>
+        <v>2186.313881748916</v>
       </c>
       <c r="U17" t="n">
-        <v>1858.889943810873</v>
+        <v>1854.889943810874</v>
       </c>
       <c r="V17" t="n">
-        <v>1546.919212329232</v>
+        <v>1542.919212329234</v>
       </c>
       <c r="W17" t="n">
-        <v>1226.339943661608</v>
+        <v>1222.33994366161</v>
       </c>
       <c r="X17" t="n">
-        <v>952.317889660934</v>
+        <v>948.3178896609356</v>
       </c>
       <c r="Y17" t="n">
-        <v>760.0780586682004</v>
+        <v>756.0780586682019</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1326.120017598837</v>
+        <v>168.3033844885911</v>
       </c>
       <c r="C18" t="n">
-        <v>961.3726312902318</v>
+        <v>127.79842242241</v>
       </c>
       <c r="D18" t="n">
-        <v>934.1628465450776</v>
+        <v>100.5886376772558</v>
       </c>
       <c r="E18" t="n">
-        <v>596.3824226873588</v>
+        <v>78.69763038239458</v>
       </c>
       <c r="F18" t="n">
-        <v>577.5579354773822</v>
+        <v>59.87314317241795</v>
       </c>
       <c r="G18" t="n">
-        <v>249.2820177839106</v>
+        <v>55.83964972137071</v>
       </c>
       <c r="H18" t="n">
-        <v>245.2823680625399</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I18" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J18" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K18" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L18" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M18" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N18" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O18" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P18" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R18" t="n">
-        <v>2071.479071663636</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S18" t="n">
-        <v>1938.448397028141</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T18" t="n">
-        <v>1856.277345826917</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U18" t="n">
-        <v>1776.316481193986</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V18" t="n">
-        <v>1681.861261808612</v>
+        <v>1496.771901425639</v>
       </c>
       <c r="W18" t="n">
-        <v>1569.36313765727</v>
+        <v>1060.031353031873</v>
       </c>
       <c r="X18" t="n">
-        <v>1469.501784682131</v>
+        <v>635.9275758143093</v>
       </c>
       <c r="Y18" t="n">
-        <v>1390.318559665834</v>
+        <v>232.5019265555877</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>681.5388756890411</v>
+        <v>686.5872726401018</v>
       </c>
       <c r="C19" t="n">
-        <v>729.3308815074769</v>
+        <v>734.3792784585376</v>
       </c>
       <c r="D19" t="n">
-        <v>764.4400256324769</v>
+        <v>769.4884225835376</v>
       </c>
       <c r="E19" t="n">
-        <v>804.0589298438899</v>
+        <v>809.1073267949506</v>
       </c>
       <c r="F19" t="n">
-        <v>850.2099024358254</v>
+        <v>855.2582993868861</v>
       </c>
       <c r="G19" t="n">
-        <v>926.0259486505795</v>
+        <v>931.0743456016402</v>
       </c>
       <c r="H19" t="n">
-        <v>1022.840277088666</v>
+        <v>1027.888674039726</v>
       </c>
       <c r="I19" t="n">
-        <v>1184.392618975568</v>
+        <v>1189.441015926629</v>
       </c>
       <c r="J19" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K19" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L19" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M19" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N19" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O19" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P19" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568783</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380925</v>
       </c>
       <c r="R19" t="n">
-        <v>82.69634147829412</v>
+        <v>82.61634147829417</v>
       </c>
       <c r="S19" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="T19" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506082</v>
       </c>
       <c r="U19" t="n">
-        <v>327.6791351738997</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V19" t="n">
-        <v>448.2905280598457</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W19" t="n">
-        <v>541.9714463195231</v>
+        <v>547.0198432705838</v>
       </c>
       <c r="X19" t="n">
-        <v>614.7922373437167</v>
+        <v>619.8406342947774</v>
       </c>
       <c r="Y19" t="n">
-        <v>647.991538022749</v>
+        <v>653.0399349738096</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>596.5184060421567</v>
+        <v>593.4524900262329</v>
       </c>
       <c r="C20" t="n">
-        <v>466.7461047866073</v>
+        <v>463.6801887706835</v>
       </c>
       <c r="D20" t="n">
-        <v>376.5045333322136</v>
+        <v>373.4386173162897</v>
       </c>
       <c r="E20" t="n">
-        <v>292.2991902949725</v>
+        <v>289.2332742790487</v>
       </c>
       <c r="F20" t="n">
-        <v>207.562191600011</v>
+        <v>204.4962755840872</v>
       </c>
       <c r="G20" t="n">
-        <v>125.3779517892592</v>
+        <v>122.3120357733353</v>
       </c>
       <c r="H20" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I20" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J20" t="n">
-        <v>134.440205073642</v>
+        <v>560.3618942939372</v>
       </c>
       <c r="K20" t="n">
-        <v>310.1117798977626</v>
+        <v>736.0334691180578</v>
       </c>
       <c r="L20" t="n">
-        <v>952.6217798977626</v>
+        <v>953.9695916306206</v>
       </c>
       <c r="M20" t="n">
-        <v>1595.131779897762</v>
+        <v>1001.294971748372</v>
       </c>
       <c r="N20" t="n">
-        <v>1595.131779897762</v>
+        <v>1642.814971748373</v>
       </c>
       <c r="O20" t="n">
-        <v>1809.956778005698</v>
+        <v>1805.9567780057</v>
       </c>
       <c r="P20" t="n">
-        <v>2008.265727912157</v>
+        <v>2004.265727912159</v>
       </c>
       <c r="Q20" t="n">
-        <v>2596</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="R20" t="n">
-        <v>2595.065916015951</v>
+        <v>2592.000000000027</v>
       </c>
       <c r="S20" t="n">
-        <v>2451.570786871937</v>
+        <v>2448.504870856013</v>
       </c>
       <c r="T20" t="n">
-        <v>2189.379797764865</v>
+        <v>2186.313881748941</v>
       </c>
       <c r="U20" t="n">
-        <v>1857.955859826824</v>
+        <v>1854.8899438109</v>
       </c>
       <c r="V20" t="n">
-        <v>1545.985128345183</v>
+        <v>1542.919212329259</v>
       </c>
       <c r="W20" t="n">
-        <v>1225.405859677559</v>
+        <v>1222.339943661636</v>
       </c>
       <c r="X20" t="n">
-        <v>951.383805676885</v>
+        <v>948.3178896609611</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.1439746841512</v>
+        <v>756.0780586682274</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>168.383384488591</v>
+        <v>1326.040017598837</v>
       </c>
       <c r="C21" t="n">
-        <v>127.87842242241</v>
+        <v>1100.525695149683</v>
       </c>
       <c r="D21" t="n">
-        <v>100.6686376772558</v>
+        <v>749.0734861621044</v>
       </c>
       <c r="E21" t="n">
-        <v>78.77763038239453</v>
+        <v>402.9400546248189</v>
       </c>
       <c r="F21" t="n">
-        <v>59.95314317241791</v>
+        <v>59.87314317241795</v>
       </c>
       <c r="G21" t="n">
-        <v>55.91964972137067</v>
+        <v>55.83964972137071</v>
       </c>
       <c r="H21" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I21" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J21" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K21" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L21" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M21" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N21" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O21" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P21" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R21" t="n">
-        <v>2071.479071663636</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S21" t="n">
-        <v>1938.448397028141</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T21" t="n">
-        <v>1856.277345826917</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U21" t="n">
-        <v>1776.316481193986</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V21" t="n">
-        <v>1357.618837566188</v>
+        <v>1681.781261808612</v>
       </c>
       <c r="W21" t="n">
-        <v>920.8782891724215</v>
+        <v>1569.28313765727</v>
       </c>
       <c r="X21" t="n">
-        <v>636.0075758143092</v>
+        <v>1469.421784682131</v>
       </c>
       <c r="Y21" t="n">
-        <v>232.5819265555876</v>
+        <v>1390.238559665834</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>681.5388756890411</v>
+        <v>686.5872726401018</v>
       </c>
       <c r="C22" t="n">
-        <v>729.3308815074769</v>
+        <v>734.3792784585376</v>
       </c>
       <c r="D22" t="n">
-        <v>764.4400256324769</v>
+        <v>769.4884225835376</v>
       </c>
       <c r="E22" t="n">
-        <v>804.0589298438899</v>
+        <v>809.1073267949506</v>
       </c>
       <c r="F22" t="n">
-        <v>850.2099024358254</v>
+        <v>855.2582993868861</v>
       </c>
       <c r="G22" t="n">
-        <v>926.0259486505795</v>
+        <v>931.0743456016402</v>
       </c>
       <c r="H22" t="n">
-        <v>1022.840277088666</v>
+        <v>1027.888674039726</v>
       </c>
       <c r="I22" t="n">
-        <v>1184.392618975568</v>
+        <v>1189.441015926629</v>
       </c>
       <c r="J22" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K22" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L22" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M22" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N22" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O22" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P22" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568783</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380925</v>
       </c>
       <c r="R22" t="n">
-        <v>82.69634147829413</v>
+        <v>82.61634147829417</v>
       </c>
       <c r="S22" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="T22" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506082</v>
       </c>
       <c r="U22" t="n">
-        <v>327.6791351738997</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V22" t="n">
-        <v>448.2905280598457</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W22" t="n">
-        <v>541.9714463195231</v>
+        <v>547.0198432705838</v>
       </c>
       <c r="X22" t="n">
-        <v>614.7922373437167</v>
+        <v>619.8406342947774</v>
       </c>
       <c r="Y22" t="n">
-        <v>647.991538022749</v>
+        <v>653.0399349738096</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>597.4524900262056</v>
+        <v>596.4384060421568</v>
       </c>
       <c r="C23" t="n">
-        <v>467.6801887706562</v>
+        <v>466.6661047866074</v>
       </c>
       <c r="D23" t="n">
-        <v>377.4386173162624</v>
+        <v>376.4245333322136</v>
       </c>
       <c r="E23" t="n">
-        <v>293.2332742790214</v>
+        <v>292.2191902949726</v>
       </c>
       <c r="F23" t="n">
-        <v>208.4962755840599</v>
+        <v>207.4821916000111</v>
       </c>
       <c r="G23" t="n">
-        <v>126.3120357733081</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H23" t="n">
-        <v>52.85408398404886</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I23" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J23" t="n">
-        <v>329.6566189185526</v>
+        <v>134.360205073642</v>
       </c>
       <c r="K23" t="n">
-        <v>505.3281937426732</v>
+        <v>729.5731213236521</v>
       </c>
       <c r="L23" t="n">
-        <v>1147.838193742673</v>
+        <v>947.5092438362149</v>
       </c>
       <c r="M23" t="n">
-        <v>1790.348193742673</v>
+        <v>1589.029243836215</v>
       </c>
       <c r="N23" t="n">
-        <v>1790.348193742673</v>
+        <v>2230.549243836216</v>
       </c>
       <c r="O23" t="n">
-        <v>1953.49</v>
+        <v>2393.691050093543</v>
       </c>
       <c r="P23" t="n">
-        <v>2596</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="Q23" t="n">
-        <v>2596</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="R23" t="n">
-        <v>2596</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="S23" t="n">
-        <v>2452.504870855986</v>
+        <v>2448.504870855988</v>
       </c>
       <c r="T23" t="n">
-        <v>2190.313881748914</v>
+        <v>2186.313881748916</v>
       </c>
       <c r="U23" t="n">
-        <v>1858.889943810872</v>
+        <v>1854.889943810874</v>
       </c>
       <c r="V23" t="n">
-        <v>1546.919212329232</v>
+        <v>1542.919212329234</v>
       </c>
       <c r="W23" t="n">
-        <v>1226.339943661608</v>
+        <v>1222.33994366161</v>
       </c>
       <c r="X23" t="n">
-        <v>952.3178896609338</v>
+        <v>948.3178896609356</v>
       </c>
       <c r="Y23" t="n">
-        <v>760.0780586682001</v>
+        <v>756.0780586682019</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>168.383384488591</v>
+        <v>168.3033844885911</v>
       </c>
       <c r="C24" t="n">
-        <v>127.87842242241</v>
+        <v>127.79842242241</v>
       </c>
       <c r="D24" t="n">
-        <v>100.6686376772558</v>
+        <v>100.5886376772558</v>
       </c>
       <c r="E24" t="n">
-        <v>78.77763038239453</v>
+        <v>78.69763038239458</v>
       </c>
       <c r="F24" t="n">
-        <v>59.95314317241791</v>
+        <v>59.87314317241795</v>
       </c>
       <c r="G24" t="n">
-        <v>55.91964972137067</v>
+        <v>55.83964972137071</v>
       </c>
       <c r="H24" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I24" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J24" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K24" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L24" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M24" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N24" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O24" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P24" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R24" t="n">
-        <v>2071.479071663636</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S24" t="n">
-        <v>1938.448397028141</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T24" t="n">
-        <v>1671.267985443944</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U24" t="n">
-        <v>1267.064696568588</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V24" t="n">
-        <v>1172.609477183214</v>
+        <v>1496.771901425639</v>
       </c>
       <c r="W24" t="n">
-        <v>735.8689287894482</v>
+        <v>1060.031353031873</v>
       </c>
       <c r="X24" t="n">
-        <v>311.765151571885</v>
+        <v>635.9275758143093</v>
       </c>
       <c r="Y24" t="n">
-        <v>232.5819265555876</v>
+        <v>232.5019265555877</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>681.5388756890411</v>
+        <v>686.5872726401018</v>
       </c>
       <c r="C25" t="n">
-        <v>729.3308815074769</v>
+        <v>734.3792784585376</v>
       </c>
       <c r="D25" t="n">
-        <v>764.4400256324769</v>
+        <v>769.4884225835376</v>
       </c>
       <c r="E25" t="n">
-        <v>804.0589298438899</v>
+        <v>809.1073267949506</v>
       </c>
       <c r="F25" t="n">
-        <v>850.2099024358254</v>
+        <v>855.2582993868861</v>
       </c>
       <c r="G25" t="n">
-        <v>926.0259486505795</v>
+        <v>931.0743456016402</v>
       </c>
       <c r="H25" t="n">
-        <v>1022.840277088666</v>
+        <v>1027.888674039726</v>
       </c>
       <c r="I25" t="n">
-        <v>1184.392618975568</v>
+        <v>1189.441015926629</v>
       </c>
       <c r="J25" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K25" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L25" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M25" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N25" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O25" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P25" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568783</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380925</v>
       </c>
       <c r="R25" t="n">
-        <v>82.69634147829413</v>
+        <v>82.61634147829417</v>
       </c>
       <c r="S25" t="n">
-        <v>51.92</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="T25" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506082</v>
       </c>
       <c r="U25" t="n">
-        <v>332.8075321249603</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V25" t="n">
-        <v>453.4189250109063</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W25" t="n">
-        <v>541.9714463195231</v>
+        <v>547.0198432705838</v>
       </c>
       <c r="X25" t="n">
-        <v>614.7922373437167</v>
+        <v>619.8406342947774</v>
       </c>
       <c r="Y25" t="n">
-        <v>647.991538022749</v>
+        <v>653.0399349738096</v>
       </c>
     </row>
     <row r="26">
@@ -6223,16 +6223,16 @@
         <v>1202.951894293937</v>
       </c>
       <c r="L26" t="n">
-        <v>1790.348193742673</v>
+        <v>1845.461894293937</v>
       </c>
       <c r="M26" t="n">
-        <v>1790.348193742673</v>
+        <v>2234.549243836214</v>
       </c>
       <c r="N26" t="n">
-        <v>1790.348193742673</v>
+        <v>2234.549243836214</v>
       </c>
       <c r="O26" t="n">
-        <v>1953.49</v>
+        <v>2397.691050093541</v>
       </c>
       <c r="P26" t="n">
         <v>2596</v>
@@ -6272,25 +6272,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>923.2868357845546</v>
+        <v>1326.120017598837</v>
       </c>
       <c r="C27" t="n">
-        <v>882.7818737183735</v>
+        <v>961.3726312902318</v>
       </c>
       <c r="D27" t="n">
-        <v>855.5720889732194</v>
+        <v>934.1628465450776</v>
       </c>
       <c r="E27" t="n">
-        <v>509.4386574359339</v>
+        <v>727.2624788672431</v>
       </c>
       <c r="F27" t="n">
-        <v>166.3717459835329</v>
+        <v>708.4379916572665</v>
       </c>
       <c r="G27" t="n">
-        <v>162.3382525324857</v>
+        <v>380.162073963795</v>
       </c>
       <c r="H27" t="n">
-        <v>158.338602811115</v>
+        <v>51.92</v>
       </c>
       <c r="I27" t="n">
         <v>51.92</v>
@@ -6317,31 +6317,31 @@
         <v>2253.229505368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>2174.638747796677</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="R27" t="n">
-        <v>1992.888314091777</v>
+        <v>2071.479071663636</v>
       </c>
       <c r="S27" t="n">
-        <v>1859.857639456283</v>
+        <v>1938.448397028141</v>
       </c>
       <c r="T27" t="n">
-        <v>1777.686588255059</v>
+        <v>1856.277345826917</v>
       </c>
       <c r="U27" t="n">
-        <v>1697.725723622128</v>
+        <v>1776.316481193986</v>
       </c>
       <c r="V27" t="n">
-        <v>1603.270504236754</v>
+        <v>1681.861261808612</v>
       </c>
       <c r="W27" t="n">
-        <v>1490.772380085412</v>
+        <v>1569.36313765727</v>
       </c>
       <c r="X27" t="n">
-        <v>1066.668602867848</v>
+        <v>1469.501784682131</v>
       </c>
       <c r="Y27" t="n">
-        <v>987.4853778515511</v>
+        <v>1390.318559665834</v>
       </c>
     </row>
     <row r="28">
@@ -6351,31 +6351,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>681.5388756890411</v>
+        <v>686.6672726401017</v>
       </c>
       <c r="C28" t="n">
-        <v>729.3308815074769</v>
+        <v>734.4592784585375</v>
       </c>
       <c r="D28" t="n">
-        <v>764.4400256324769</v>
+        <v>769.5684225835375</v>
       </c>
       <c r="E28" t="n">
-        <v>804.0589298438899</v>
+        <v>809.1873267949505</v>
       </c>
       <c r="F28" t="n">
-        <v>850.2099024358254</v>
+        <v>855.338299386886</v>
       </c>
       <c r="G28" t="n">
-        <v>926.0259486505795</v>
+        <v>931.1543456016401</v>
       </c>
       <c r="H28" t="n">
-        <v>1022.840277088666</v>
+        <v>1027.968674039726</v>
       </c>
       <c r="I28" t="n">
-        <v>1184.392618975568</v>
+        <v>1189.521015926629</v>
       </c>
       <c r="J28" t="n">
-        <v>1511.063618808347</v>
+        <v>1516.192015759408</v>
       </c>
       <c r="K28" t="n">
         <v>1615.190403564888</v>
@@ -6408,19 +6408,19 @@
         <v>164.4325496506081</v>
       </c>
       <c r="U28" t="n">
-        <v>327.6791351738997</v>
+        <v>332.8075321249603</v>
       </c>
       <c r="V28" t="n">
-        <v>448.2905280598457</v>
+        <v>453.4189250109063</v>
       </c>
       <c r="W28" t="n">
-        <v>541.9714463195231</v>
+        <v>547.0998432705837</v>
       </c>
       <c r="X28" t="n">
-        <v>614.7922373437167</v>
+        <v>619.9206342947773</v>
       </c>
       <c r="Y28" t="n">
-        <v>647.991538022749</v>
+        <v>653.1199349738096</v>
       </c>
     </row>
     <row r="29">
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>596.5184060421568</v>
+        <v>597.4524900262059</v>
       </c>
       <c r="C29" t="n">
-        <v>466.7461047866074</v>
+        <v>467.6801887706564</v>
       </c>
       <c r="D29" t="n">
-        <v>376.5045333322136</v>
+        <v>377.4386173162627</v>
       </c>
       <c r="E29" t="n">
-        <v>292.2991902949726</v>
+        <v>293.2332742790216</v>
       </c>
       <c r="F29" t="n">
-        <v>207.5621916000111</v>
+        <v>208.4962755840601</v>
       </c>
       <c r="G29" t="n">
-        <v>125.3779517892592</v>
+        <v>126.3120357733083</v>
       </c>
       <c r="H29" t="n">
         <v>51.92</v>
@@ -6454,52 +6454,52 @@
         <v>51.92</v>
       </c>
       <c r="J29" t="n">
-        <v>560.4418942939371</v>
+        <v>134.440205073642</v>
       </c>
       <c r="K29" t="n">
-        <v>1202.951894293937</v>
+        <v>776.950205073642</v>
       </c>
       <c r="L29" t="n">
-        <v>1755.181050093541</v>
+        <v>994.8863275862049</v>
       </c>
       <c r="M29" t="n">
-        <v>1755.181050093541</v>
+        <v>1637.396327586205</v>
       </c>
       <c r="N29" t="n">
-        <v>1755.181050093541</v>
+        <v>1646.814971748371</v>
       </c>
       <c r="O29" t="n">
-        <v>2397.691050093541</v>
+        <v>1809.956778005698</v>
       </c>
       <c r="P29" t="n">
-        <v>2596</v>
+        <v>2008.265727912157</v>
       </c>
       <c r="Q29" t="n">
         <v>2596</v>
       </c>
       <c r="R29" t="n">
-        <v>2595.065916015951</v>
+        <v>2596</v>
       </c>
       <c r="S29" t="n">
-        <v>2451.570786871937</v>
+        <v>2452.504870855986</v>
       </c>
       <c r="T29" t="n">
-        <v>2189.379797764865</v>
+        <v>2190.313881748914</v>
       </c>
       <c r="U29" t="n">
-        <v>1857.955859826824</v>
+        <v>1858.889943810873</v>
       </c>
       <c r="V29" t="n">
-        <v>1545.985128345183</v>
+        <v>1546.919212329232</v>
       </c>
       <c r="W29" t="n">
-        <v>1225.405859677559</v>
+        <v>1226.339943661608</v>
       </c>
       <c r="X29" t="n">
-        <v>951.383805676885</v>
+        <v>952.317889660934</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.1439746841513</v>
+        <v>760.0780586682004</v>
       </c>
     </row>
     <row r="30">
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>816.8682329734396</v>
+        <v>168.3833844885911</v>
       </c>
       <c r="C30" t="n">
-        <v>776.3632709072585</v>
+        <v>127.87842242241</v>
       </c>
       <c r="D30" t="n">
-        <v>424.9110619196801</v>
+        <v>100.6686376772558</v>
       </c>
       <c r="E30" t="n">
-        <v>403.0200546248188</v>
+        <v>78.77763038239456</v>
       </c>
       <c r="F30" t="n">
-        <v>384.1955674148422</v>
+        <v>59.95314317241794</v>
       </c>
       <c r="G30" t="n">
-        <v>380.162073963795</v>
+        <v>55.91964972137069</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6569,16 +6569,16 @@
         <v>1776.316481193986</v>
       </c>
       <c r="V30" t="n">
-        <v>1681.861261808612</v>
+        <v>1357.618837566188</v>
       </c>
       <c r="W30" t="n">
-        <v>1384.353777274297</v>
+        <v>1060.111353031873</v>
       </c>
       <c r="X30" t="n">
-        <v>960.2500000567335</v>
+        <v>636.0075758143092</v>
       </c>
       <c r="Y30" t="n">
-        <v>881.0667750404361</v>
+        <v>556.8243507980119</v>
       </c>
     </row>
     <row r="31">
@@ -6594,22 +6594,22 @@
         <v>734.4592784585375</v>
       </c>
       <c r="D31" t="n">
-        <v>769.5684225835375</v>
+        <v>764.4400256324769</v>
       </c>
       <c r="E31" t="n">
-        <v>809.1873267949505</v>
+        <v>804.0589298438899</v>
       </c>
       <c r="F31" t="n">
-        <v>855.338299386886</v>
+        <v>850.2099024358254</v>
       </c>
       <c r="G31" t="n">
-        <v>931.1543456016401</v>
+        <v>926.0259486505795</v>
       </c>
       <c r="H31" t="n">
-        <v>1027.968674039726</v>
+        <v>1022.840277088666</v>
       </c>
       <c r="I31" t="n">
-        <v>1189.521015926629</v>
+        <v>1184.392618975568</v>
       </c>
       <c r="J31" t="n">
         <v>1511.063618808347</v>
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>597.4524900262056</v>
+        <v>596.5184060421568</v>
       </c>
       <c r="C32" t="n">
-        <v>467.6801887706562</v>
+        <v>466.7461047866074</v>
       </c>
       <c r="D32" t="n">
-        <v>377.4386173162624</v>
+        <v>376.5045333322136</v>
       </c>
       <c r="E32" t="n">
-        <v>293.2332742790214</v>
+        <v>292.2991902949726</v>
       </c>
       <c r="F32" t="n">
-        <v>208.4962755840599</v>
+        <v>207.5621916000111</v>
       </c>
       <c r="G32" t="n">
-        <v>126.3120357733081</v>
+        <v>125.3779517892592</v>
       </c>
       <c r="H32" t="n">
         <v>51.92</v>
@@ -6697,16 +6697,16 @@
         <v>310.1117798977626</v>
       </c>
       <c r="L32" t="n">
-        <v>723.2457279121568</v>
+        <v>528.0479024103255</v>
       </c>
       <c r="M32" t="n">
-        <v>723.2457279121568</v>
+        <v>1170.557902410325</v>
       </c>
       <c r="N32" t="n">
-        <v>723.2457279121568</v>
+        <v>1646.814971748371</v>
       </c>
       <c r="O32" t="n">
-        <v>1365.755727912157</v>
+        <v>1809.956778005698</v>
       </c>
       <c r="P32" t="n">
         <v>2008.265727912157</v>
@@ -6724,19 +6724,19 @@
         <v>2190.313881748914</v>
       </c>
       <c r="U32" t="n">
-        <v>1858.889943810872</v>
+        <v>1857.955859826824</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.919212329232</v>
+        <v>1545.985128345183</v>
       </c>
       <c r="W32" t="n">
-        <v>1226.339943661608</v>
+        <v>1225.405859677559</v>
       </c>
       <c r="X32" t="n">
-        <v>952.3178896609338</v>
+        <v>951.383805676885</v>
       </c>
       <c r="Y32" t="n">
-        <v>760.0780586682001</v>
+        <v>759.1439746841513</v>
       </c>
     </row>
     <row r="33">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>168.383384488591</v>
+        <v>1001.877593356413</v>
       </c>
       <c r="C33" t="n">
-        <v>127.87842242241</v>
+        <v>637.1302070478075</v>
       </c>
       <c r="D33" t="n">
-        <v>100.6686376772558</v>
+        <v>285.6779980602291</v>
       </c>
       <c r="E33" t="n">
-        <v>78.77763038239453</v>
+        <v>78.77763038239456</v>
       </c>
       <c r="F33" t="n">
-        <v>59.95314317241791</v>
+        <v>59.95314317241794</v>
       </c>
       <c r="G33" t="n">
-        <v>55.91964972137067</v>
+        <v>55.91964972137069</v>
       </c>
       <c r="H33" t="n">
         <v>51.92</v>
@@ -6794,28 +6794,28 @@
         <v>2253.229505368536</v>
       </c>
       <c r="R33" t="n">
-        <v>1747.236647421212</v>
+        <v>2071.479071663636</v>
       </c>
       <c r="S33" t="n">
-        <v>1429.196612402744</v>
+        <v>1938.448397028141</v>
       </c>
       <c r="T33" t="n">
-        <v>1022.783136959095</v>
+        <v>1856.277345826917</v>
       </c>
       <c r="U33" t="n">
-        <v>942.8222723261641</v>
+        <v>1776.316481193986</v>
       </c>
       <c r="V33" t="n">
-        <v>848.3670529407902</v>
+        <v>1681.861261808612</v>
       </c>
       <c r="W33" t="n">
-        <v>411.626504547024</v>
+        <v>1569.36313765727</v>
       </c>
       <c r="X33" t="n">
-        <v>311.765151571885</v>
+        <v>1469.501784682131</v>
       </c>
       <c r="Y33" t="n">
-        <v>232.5819265555876</v>
+        <v>1390.318559665834</v>
       </c>
     </row>
     <row r="34">
@@ -6825,28 +6825,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>681.5388756890411</v>
+        <v>686.6672726401017</v>
       </c>
       <c r="C34" t="n">
-        <v>729.3308815074769</v>
+        <v>734.4592784585375</v>
       </c>
       <c r="D34" t="n">
-        <v>764.4400256324769</v>
+        <v>769.5684225835375</v>
       </c>
       <c r="E34" t="n">
-        <v>804.0589298438899</v>
+        <v>809.1873267949505</v>
       </c>
       <c r="F34" t="n">
-        <v>850.2099024358254</v>
+        <v>855.338299386886</v>
       </c>
       <c r="G34" t="n">
-        <v>926.0259486505795</v>
+        <v>931.1543456016401</v>
       </c>
       <c r="H34" t="n">
-        <v>1022.840277088666</v>
+        <v>1027.968674039726</v>
       </c>
       <c r="I34" t="n">
-        <v>1184.392618975568</v>
+        <v>1189.521015926629</v>
       </c>
       <c r="J34" t="n">
         <v>1511.063618808347</v>
@@ -6873,7 +6873,7 @@
         <v>463.9758216380924</v>
       </c>
       <c r="R34" t="n">
-        <v>82.69634147829413</v>
+        <v>82.69634147829412</v>
       </c>
       <c r="S34" t="n">
         <v>51.92</v>
@@ -6894,7 +6894,7 @@
         <v>619.9206342947773</v>
       </c>
       <c r="Y34" t="n">
-        <v>647.991538022749</v>
+        <v>653.1199349738096</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>443.3918839655994</v>
+        <v>439.3918839655994</v>
       </c>
       <c r="C35" t="n">
-        <v>337.8620069524742</v>
+        <v>333.8620069524742</v>
       </c>
       <c r="D35" t="n">
-        <v>271.8628597405047</v>
+        <v>267.8628597405047</v>
       </c>
       <c r="E35" t="n">
-        <v>211.8999409456879</v>
+        <v>207.8999409456879</v>
       </c>
       <c r="F35" t="n">
-        <v>151.4053664931506</v>
+        <v>147.4053664931506</v>
       </c>
       <c r="G35" t="n">
-        <v>94.17552754683496</v>
+        <v>94.09552754683496</v>
       </c>
       <c r="H35" t="n">
-        <v>44.96</v>
+        <v>44.88</v>
       </c>
       <c r="I35" t="n">
-        <v>44.96</v>
+        <v>44.88</v>
       </c>
       <c r="J35" t="n">
-        <v>553.4818942939371</v>
+        <v>553.4018942939372</v>
       </c>
       <c r="K35" t="n">
-        <v>729.1534691180577</v>
+        <v>729.0734691180577</v>
       </c>
       <c r="L35" t="n">
-        <v>947.0895916306206</v>
+        <v>947.0095916306205</v>
       </c>
       <c r="M35" t="n">
-        <v>972.0981937426731</v>
+        <v>970.0781937426733</v>
       </c>
       <c r="N35" t="n">
-        <v>1528.478193742673</v>
+        <v>1525.468193742673</v>
       </c>
       <c r="O35" t="n">
-        <v>1691.62</v>
+        <v>1688.61</v>
       </c>
       <c r="P35" t="n">
-        <v>2248</v>
+        <v>2244</v>
       </c>
       <c r="Q35" t="n">
-        <v>2248</v>
+        <v>2244</v>
       </c>
       <c r="R35" t="n">
-        <v>2248</v>
+        <v>2244</v>
       </c>
       <c r="S35" t="n">
-        <v>2128.74729509841</v>
+        <v>2124.74729509841</v>
       </c>
       <c r="T35" t="n">
-        <v>1890.798730233762</v>
+        <v>1886.798730233762</v>
       </c>
       <c r="U35" t="n">
-        <v>1583.617216538145</v>
+        <v>1579.617216538145</v>
       </c>
       <c r="V35" t="n">
-        <v>1295.888909298929</v>
+        <v>1291.888909298929</v>
       </c>
       <c r="W35" t="n">
-        <v>999.5520648737293</v>
+        <v>995.5520648737293</v>
       </c>
       <c r="X35" t="n">
-        <v>749.7724351154791</v>
+        <v>745.7724351154791</v>
       </c>
       <c r="Y35" t="n">
-        <v>581.7750283651696</v>
+        <v>577.7750283651696</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>257.5522663890268</v>
+        <v>64.10989832648681</v>
       </c>
       <c r="C36" t="n">
-        <v>241.2897285652699</v>
+        <v>47.84736050272995</v>
       </c>
       <c r="D36" t="n">
-        <v>238.32236806254</v>
+        <v>44.88</v>
       </c>
       <c r="E36" t="n">
-        <v>238.32236806254</v>
+        <v>44.88</v>
       </c>
       <c r="F36" t="n">
-        <v>238.32236806254</v>
+        <v>44.88</v>
       </c>
       <c r="G36" t="n">
-        <v>238.32236806254</v>
+        <v>44.88</v>
       </c>
       <c r="H36" t="n">
-        <v>238.32236806254</v>
+        <v>44.88</v>
       </c>
       <c r="I36" t="n">
-        <v>44.96</v>
+        <v>44.88</v>
       </c>
       <c r="J36" t="n">
-        <v>238.7276497036009</v>
+        <v>238.6476497036008</v>
       </c>
       <c r="K36" t="n">
-        <v>547.2388055149654</v>
+        <v>547.1588055149654</v>
       </c>
       <c r="L36" t="n">
-        <v>979.0274996573354</v>
+        <v>976.7579942888729</v>
       </c>
       <c r="M36" t="n">
-        <v>1252.331891400195</v>
+        <v>1250.062386031732</v>
       </c>
       <c r="N36" t="n">
-        <v>1577.79128421531</v>
+        <v>1575.521778846848</v>
       </c>
       <c r="O36" t="n">
-        <v>1992.640074672614</v>
+        <v>1990.370569304152</v>
       </c>
       <c r="P36" t="n">
-        <v>2246.269505368536</v>
+        <v>2244.000000000073</v>
       </c>
       <c r="Q36" t="n">
-        <v>2246.269505368536</v>
+        <v>2166.976961853761</v>
       </c>
       <c r="R36" t="n">
-        <v>2088.76149590606</v>
+        <v>2009.468952391285</v>
       </c>
       <c r="S36" t="n">
-        <v>1631.488397028141</v>
+        <v>1900.680701998215</v>
       </c>
       <c r="T36" t="n">
-        <v>1573.559770069341</v>
+        <v>1842.752075039415</v>
       </c>
       <c r="U36" t="n">
-        <v>1169.356481193986</v>
+        <v>1787.033634648908</v>
       </c>
       <c r="V36" t="n">
-        <v>1099.143686051036</v>
+        <v>1368.33599102111</v>
       </c>
       <c r="W36" t="n">
-        <v>1010.887986142118</v>
+        <v>931.595442627344</v>
       </c>
       <c r="X36" t="n">
-        <v>700.9340334723207</v>
+        <v>507.4916654097808</v>
       </c>
       <c r="Y36" t="n">
-        <v>297.5083842135991</v>
+        <v>104.0660161510592</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>508.4240294245153</v>
+        <v>267.0105946885323</v>
       </c>
       <c r="C37" t="n">
-        <v>529.9082894749215</v>
+        <v>338.562600506968</v>
       </c>
       <c r="D37" t="n">
-        <v>588.7774335999216</v>
+        <v>397.4317446319681</v>
       </c>
       <c r="E37" t="n">
-        <v>588.7774335999216</v>
+        <v>460.8106488433811</v>
       </c>
       <c r="F37" t="n">
-        <v>658.688406191857</v>
+        <v>530.7216214353166</v>
       </c>
       <c r="G37" t="n">
-        <v>758.2644524066111</v>
+        <v>630.2976676500707</v>
       </c>
       <c r="H37" t="n">
-        <v>878.8387808446972</v>
+        <v>750.8719960881568</v>
       </c>
       <c r="I37" t="n">
-        <v>1064.1511227316</v>
+        <v>936.1843379750594</v>
       </c>
       <c r="J37" t="n">
-        <v>1414.582122564379</v>
+        <v>1286.615337807839</v>
       </c>
       <c r="K37" t="n">
-        <v>1414.582122564379</v>
+        <v>1414.502122564379</v>
       </c>
       <c r="L37" t="n">
-        <v>1428.919800524243</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="M37" t="n">
-        <v>1350.592142045098</v>
+        <v>1350.512142045098</v>
       </c>
       <c r="N37" t="n">
-        <v>1218.844525029487</v>
+        <v>1218.764525029487</v>
       </c>
       <c r="O37" t="n">
-        <v>1009.753228311157</v>
+        <v>1009.673228311158</v>
       </c>
       <c r="P37" t="n">
-        <v>740.2908382296055</v>
+        <v>740.2108382296055</v>
       </c>
       <c r="Q37" t="n">
-        <v>408.5309731532439</v>
+        <v>408.4509731532439</v>
       </c>
       <c r="R37" t="n">
-        <v>51.49391723586989</v>
+        <v>51.41391723586989</v>
       </c>
       <c r="S37" t="n">
-        <v>44.96</v>
+        <v>44.88</v>
       </c>
       <c r="T37" t="n">
-        <v>44.96</v>
+        <v>56.16316531901434</v>
       </c>
       <c r="U37" t="n">
-        <v>237.0949824743522</v>
+        <v>56.16316531901434</v>
       </c>
       <c r="V37" t="n">
-        <v>237.0949824743522</v>
+        <v>56.16316531901434</v>
       </c>
       <c r="W37" t="n">
-        <v>354.5359007340297</v>
+        <v>56.16316531901434</v>
       </c>
       <c r="X37" t="n">
-        <v>451.1166917582232</v>
+        <v>152.7439563432079</v>
       </c>
       <c r="Y37" t="n">
-        <v>451.1166917582232</v>
+        <v>209.7032570222401</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>444.1038605876113</v>
+        <v>444.0238605876114</v>
       </c>
       <c r="C38" t="n">
-        <v>338.5739835744861</v>
+        <v>338.4939835744862</v>
       </c>
       <c r="D38" t="n">
-        <v>272.5748363625166</v>
+        <v>272.4948363625167</v>
       </c>
       <c r="E38" t="n">
-        <v>212.6119175676998</v>
+        <v>212.5319175676998</v>
       </c>
       <c r="F38" t="n">
-        <v>152.1173431151626</v>
+        <v>152.0373431151626</v>
       </c>
       <c r="G38" t="n">
-        <v>94.17552754683497</v>
+        <v>94.09552754683497</v>
       </c>
       <c r="H38" t="n">
-        <v>44.96</v>
+        <v>44.88</v>
       </c>
       <c r="I38" t="n">
-        <v>44.96</v>
+        <v>44.88</v>
       </c>
       <c r="J38" t="n">
-        <v>127.480205073642</v>
+        <v>127.400205073642</v>
       </c>
       <c r="K38" t="n">
-        <v>360.923877487437</v>
+        <v>303.0717798977627</v>
       </c>
       <c r="L38" t="n">
-        <v>578.8599999999998</v>
+        <v>521.0079024103255</v>
       </c>
       <c r="M38" t="n">
-        <v>578.8599999999998</v>
+        <v>1076.397902410326</v>
       </c>
       <c r="N38" t="n">
-        <v>578.8599999999998</v>
+        <v>1525.468193742673</v>
       </c>
       <c r="O38" t="n">
-        <v>1135.24</v>
+        <v>1688.61</v>
       </c>
       <c r="P38" t="n">
-        <v>1691.62</v>
+        <v>2244</v>
       </c>
       <c r="Q38" t="n">
-        <v>2248</v>
+        <v>2244</v>
       </c>
       <c r="R38" t="n">
-        <v>2248</v>
+        <v>2244.000000000066</v>
       </c>
       <c r="S38" t="n">
-        <v>2129.459271720421</v>
+        <v>2129.379271720421</v>
       </c>
       <c r="T38" t="n">
-        <v>1891.510706855774</v>
+        <v>1891.430706855774</v>
       </c>
       <c r="U38" t="n">
-        <v>1584.329193160157</v>
+        <v>1584.249193160157</v>
       </c>
       <c r="V38" t="n">
-        <v>1296.600885920941</v>
+        <v>1296.520885920941</v>
       </c>
       <c r="W38" t="n">
-        <v>1000.264041495741</v>
+        <v>1000.184041495741</v>
       </c>
       <c r="X38" t="n">
-        <v>750.484411737491</v>
+        <v>750.404411737491</v>
       </c>
       <c r="Y38" t="n">
-        <v>582.4870049871815</v>
+        <v>582.4070049871816</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>758.8081783486208</v>
+        <v>759.5118758706301</v>
       </c>
       <c r="C39" t="n">
-        <v>394.0607920400154</v>
+        <v>394.7644895620247</v>
       </c>
       <c r="D39" t="n">
-        <v>391.0934315372855</v>
+        <v>391.7971290592948</v>
       </c>
       <c r="E39" t="n">
-        <v>44.96</v>
+        <v>45.66369752200927</v>
       </c>
       <c r="F39" t="n">
-        <v>44.96</v>
+        <v>45.66369752200927</v>
       </c>
       <c r="G39" t="n">
-        <v>44.96</v>
+        <v>45.66369752200927</v>
       </c>
       <c r="H39" t="n">
-        <v>44.96</v>
+        <v>45.66369752200927</v>
       </c>
       <c r="I39" t="n">
-        <v>44.96</v>
+        <v>44.88</v>
       </c>
       <c r="J39" t="n">
-        <v>238.7276497036009</v>
+        <v>238.6476497036008</v>
       </c>
       <c r="K39" t="n">
-        <v>547.2388055149654</v>
+        <v>547.1588055149654</v>
       </c>
       <c r="L39" t="n">
-        <v>979.0274996573354</v>
+        <v>976.7579942888656</v>
       </c>
       <c r="M39" t="n">
-        <v>1252.331891400195</v>
+        <v>1250.062386031725</v>
       </c>
       <c r="N39" t="n">
-        <v>1577.79128421531</v>
+        <v>1575.52177884684</v>
       </c>
       <c r="O39" t="n">
-        <v>1992.640074672614</v>
+        <v>1990.370569304144</v>
       </c>
       <c r="P39" t="n">
-        <v>2246.269505368536</v>
+        <v>2244.000000000066</v>
       </c>
       <c r="Q39" t="n">
-        <v>2246.269505368536</v>
+        <v>2165.409242428208</v>
       </c>
       <c r="R39" t="n">
-        <v>2088.76149590606</v>
+        <v>2007.901232965732</v>
       </c>
       <c r="S39" t="n">
-        <v>1979.973245512989</v>
+        <v>1899.112982572662</v>
       </c>
       <c r="T39" t="n">
-        <v>1922.04461855419</v>
+        <v>1841.184355613862</v>
       </c>
       <c r="U39" t="n">
-        <v>1866.326178163683</v>
+        <v>1785.465915223355</v>
       </c>
       <c r="V39" t="n">
-        <v>1714.549422558395</v>
+        <v>1715.253120080405</v>
       </c>
       <c r="W39" t="n">
-        <v>1626.293722649478</v>
+        <v>1626.997420171487</v>
       </c>
       <c r="X39" t="n">
-        <v>1202.189945431915</v>
+        <v>1551.378491438773</v>
       </c>
       <c r="Y39" t="n">
-        <v>1147.249144658042</v>
+        <v>1147.952842180051</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>467.4227172239035</v>
+        <v>401.941504718381</v>
       </c>
       <c r="C40" t="n">
-        <v>467.4227172239035</v>
+        <v>401.941504718381</v>
       </c>
       <c r="D40" t="n">
-        <v>467.4227172239035</v>
+        <v>460.8106488433811</v>
       </c>
       <c r="E40" t="n">
-        <v>530.8016214353165</v>
+        <v>460.8106488433811</v>
       </c>
       <c r="F40" t="n">
-        <v>530.8016214353165</v>
+        <v>530.7216214353166</v>
       </c>
       <c r="G40" t="n">
-        <v>630.3776676500706</v>
+        <v>630.2976676500707</v>
       </c>
       <c r="H40" t="n">
-        <v>750.9519960881568</v>
+        <v>750.8719960881568</v>
       </c>
       <c r="I40" t="n">
-        <v>936.2643379750593</v>
+        <v>936.1843379750594</v>
       </c>
       <c r="J40" t="n">
-        <v>1286.695337807839</v>
+        <v>1286.615337807839</v>
       </c>
       <c r="K40" t="n">
-        <v>1414.582122564379</v>
+        <v>1414.502122564379</v>
       </c>
       <c r="L40" t="n">
-        <v>1428.919800524243</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="M40" t="n">
-        <v>1350.592142045098</v>
+        <v>1350.512142045098</v>
       </c>
       <c r="N40" t="n">
-        <v>1218.844525029487</v>
+        <v>1218.764525029487</v>
       </c>
       <c r="O40" t="n">
-        <v>1009.753228311157</v>
+        <v>1009.673228311158</v>
       </c>
       <c r="P40" t="n">
-        <v>740.2908382296055</v>
+        <v>740.2108382296055</v>
       </c>
       <c r="Q40" t="n">
-        <v>408.5309731532438</v>
+        <v>408.4509731532439</v>
       </c>
       <c r="R40" t="n">
-        <v>51.49391723586987</v>
+        <v>51.41391723586987</v>
       </c>
       <c r="S40" t="n">
-        <v>44.96</v>
+        <v>44.88</v>
       </c>
       <c r="T40" t="n">
-        <v>181.2325496506081</v>
+        <v>181.1525496506081</v>
       </c>
       <c r="U40" t="n">
-        <v>373.3675321249603</v>
+        <v>344.6341670520889</v>
       </c>
       <c r="V40" t="n">
-        <v>410.4634165448712</v>
+        <v>344.6341670520889</v>
       </c>
       <c r="W40" t="n">
-        <v>410.4634165448712</v>
+        <v>344.6341670520889</v>
       </c>
       <c r="X40" t="n">
-        <v>410.4634165448712</v>
+        <v>344.6341670520889</v>
       </c>
       <c r="Y40" t="n">
-        <v>467.4227172239035</v>
+        <v>344.6341670520889</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>444.1038605876113</v>
+        <v>444.0238605876114</v>
       </c>
       <c r="C41" t="n">
-        <v>338.5739835744861</v>
+        <v>338.4939835744862</v>
       </c>
       <c r="D41" t="n">
-        <v>272.5748363625166</v>
+        <v>272.4948363625167</v>
       </c>
       <c r="E41" t="n">
-        <v>212.6119175676998</v>
+        <v>212.5319175676998</v>
       </c>
       <c r="F41" t="n">
-        <v>152.1173431151626</v>
+        <v>152.0373431151626</v>
       </c>
       <c r="G41" t="n">
-        <v>94.17552754683496</v>
+        <v>94.09552754683497</v>
       </c>
       <c r="H41" t="n">
-        <v>44.96</v>
+        <v>44.88</v>
       </c>
       <c r="I41" t="n">
-        <v>44.96</v>
+        <v>44.88</v>
       </c>
       <c r="J41" t="n">
-        <v>127.480205073642</v>
+        <v>127.400205073642</v>
       </c>
       <c r="K41" t="n">
-        <v>303.1517798977626</v>
+        <v>303.0717798977627</v>
       </c>
       <c r="L41" t="n">
-        <v>859.5317798977626</v>
+        <v>521.0079024103255</v>
       </c>
       <c r="M41" t="n">
-        <v>1415.911779897763</v>
+        <v>1076.397902410326</v>
       </c>
       <c r="N41" t="n">
-        <v>1886.549243836214</v>
+        <v>1631.787902410325</v>
       </c>
       <c r="O41" t="n">
-        <v>2049.691050093541</v>
+        <v>1794.929708667652</v>
       </c>
       <c r="P41" t="n">
-        <v>2248</v>
+        <v>1993.238658574111</v>
       </c>
       <c r="Q41" t="n">
-        <v>2248</v>
+        <v>2244</v>
       </c>
       <c r="R41" t="n">
-        <v>2248</v>
+        <v>2244</v>
       </c>
       <c r="S41" t="n">
-        <v>2128.74729509841</v>
+        <v>2129.379271720421</v>
       </c>
       <c r="T41" t="n">
-        <v>1890.798730233762</v>
+        <v>1891.430706855774</v>
       </c>
       <c r="U41" t="n">
-        <v>1583.617216538145</v>
+        <v>1584.249193160157</v>
       </c>
       <c r="V41" t="n">
-        <v>1295.888909298929</v>
+        <v>1296.520885920941</v>
       </c>
       <c r="W41" t="n">
-        <v>999.5520648737293</v>
+        <v>1000.184041495741</v>
       </c>
       <c r="X41" t="n">
-        <v>749.7724351154791</v>
+        <v>750.404411737491</v>
       </c>
       <c r="Y41" t="n">
-        <v>581.7750283651696</v>
+        <v>582.4070049871816</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1081.666159009645</v>
+        <v>257.4722663890267</v>
       </c>
       <c r="C42" t="n">
-        <v>1065.403621185888</v>
+        <v>241.2097285652699</v>
       </c>
       <c r="D42" t="n">
-        <v>1062.436260683158</v>
+        <v>238.24236806254</v>
       </c>
       <c r="E42" t="n">
-        <v>716.3028291458725</v>
+        <v>238.24236806254</v>
       </c>
       <c r="F42" t="n">
-        <v>373.2359176934715</v>
+        <v>238.24236806254</v>
       </c>
       <c r="G42" t="n">
-        <v>44.96</v>
+        <v>238.24236806254</v>
       </c>
       <c r="H42" t="n">
-        <v>44.96</v>
+        <v>238.24236806254</v>
       </c>
       <c r="I42" t="n">
-        <v>44.96</v>
+        <v>44.88</v>
       </c>
       <c r="J42" t="n">
-        <v>238.7276497036009</v>
+        <v>238.6476497036008</v>
       </c>
       <c r="K42" t="n">
-        <v>547.2388055149654</v>
+        <v>547.1588055149654</v>
       </c>
       <c r="L42" t="n">
-        <v>979.0274996573354</v>
+        <v>978.9474996573354</v>
       </c>
       <c r="M42" t="n">
-        <v>1252.331891400195</v>
+        <v>1252.251891400195</v>
       </c>
       <c r="N42" t="n">
-        <v>1577.79128421531</v>
+        <v>1575.521778846848</v>
       </c>
       <c r="O42" t="n">
-        <v>1992.640074672614</v>
+        <v>1990.370569304152</v>
       </c>
       <c r="P42" t="n">
-        <v>2246.269505368536</v>
+        <v>2244.000000000073</v>
       </c>
       <c r="Q42" t="n">
-        <v>2246.269505368536</v>
+        <v>2165.409242428215</v>
       </c>
       <c r="R42" t="n">
-        <v>1740.276647421211</v>
+        <v>1659.416384480891</v>
       </c>
       <c r="S42" t="n">
-        <v>1631.488397028141</v>
+        <v>1550.62813408782</v>
       </c>
       <c r="T42" t="n">
-        <v>1573.559770069341</v>
+        <v>1144.214658644172</v>
       </c>
       <c r="U42" t="n">
-        <v>1410.650501392672</v>
+        <v>1088.496218253665</v>
       </c>
       <c r="V42" t="n">
-        <v>1340.437706249723</v>
+        <v>864.7286621139531</v>
       </c>
       <c r="W42" t="n">
-        <v>1252.182006340805</v>
+        <v>776.4729622050354</v>
       </c>
       <c r="X42" t="n">
-        <v>1176.56307760809</v>
+        <v>700.8540334723207</v>
       </c>
       <c r="Y42" t="n">
-        <v>1121.622276834217</v>
+        <v>645.9132326984476</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>495.7330137056226</v>
+        <v>587.2349429733852</v>
       </c>
       <c r="C43" t="n">
-        <v>567.2850195240584</v>
+        <v>658.7869487918209</v>
       </c>
       <c r="D43" t="n">
-        <v>626.1541636490584</v>
+        <v>717.656092916821</v>
       </c>
       <c r="E43" t="n">
-        <v>689.5330678604714</v>
+        <v>781.034997128234</v>
       </c>
       <c r="F43" t="n">
-        <v>689.5330678604714</v>
+        <v>850.9459697201694</v>
       </c>
       <c r="G43" t="n">
-        <v>789.1091140752255</v>
+        <v>950.5220159349235</v>
       </c>
       <c r="H43" t="n">
-        <v>789.1091140752255</v>
+        <v>950.5220159349235</v>
       </c>
       <c r="I43" t="n">
-        <v>974.4214559621281</v>
+        <v>950.5220159349235</v>
       </c>
       <c r="J43" t="n">
-        <v>1286.695337807839</v>
+        <v>1300.953015767703</v>
       </c>
       <c r="K43" t="n">
-        <v>1414.582122564379</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="L43" t="n">
-        <v>1428.919800524243</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="M43" t="n">
-        <v>1350.592142045098</v>
+        <v>1350.512142045098</v>
       </c>
       <c r="N43" t="n">
-        <v>1218.844525029487</v>
+        <v>1218.764525029487</v>
       </c>
       <c r="O43" t="n">
-        <v>1009.753228311157</v>
+        <v>1009.673228311158</v>
       </c>
       <c r="P43" t="n">
-        <v>740.2908382296055</v>
+        <v>740.2108382296055</v>
       </c>
       <c r="Q43" t="n">
-        <v>408.5309731532439</v>
+        <v>408.4509731532439</v>
       </c>
       <c r="R43" t="n">
-        <v>51.49391723586989</v>
+        <v>51.41391723586987</v>
       </c>
       <c r="S43" t="n">
-        <v>44.96</v>
+        <v>44.88</v>
       </c>
       <c r="T43" t="n">
-        <v>44.96</v>
+        <v>181.1525496506081</v>
       </c>
       <c r="U43" t="n">
-        <v>237.0949824743522</v>
+        <v>258.9465953441899</v>
       </c>
       <c r="V43" t="n">
-        <v>381.4663753602982</v>
+        <v>258.9465953441899</v>
       </c>
       <c r="W43" t="n">
-        <v>381.4663753602982</v>
+        <v>376.3875136038673</v>
       </c>
       <c r="X43" t="n">
-        <v>381.4663753602982</v>
+        <v>472.9683046280608</v>
       </c>
       <c r="Y43" t="n">
-        <v>438.4256760393305</v>
+        <v>529.927605307093</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>444.1038605876113</v>
+        <v>439.3918839655994</v>
       </c>
       <c r="C44" t="n">
-        <v>338.5739835744861</v>
+        <v>333.8620069524742</v>
       </c>
       <c r="D44" t="n">
-        <v>272.5748363625166</v>
+        <v>267.8628597405047</v>
       </c>
       <c r="E44" t="n">
-        <v>212.6119175676998</v>
+        <v>207.8999409456879</v>
       </c>
       <c r="F44" t="n">
-        <v>152.1173431151626</v>
+        <v>147.4053664931506</v>
       </c>
       <c r="G44" t="n">
-        <v>94.17552754683497</v>
+        <v>94.09552754683497</v>
       </c>
       <c r="H44" t="n">
-        <v>44.96</v>
+        <v>44.88</v>
       </c>
       <c r="I44" t="n">
-        <v>44.96</v>
+        <v>44.88</v>
       </c>
       <c r="J44" t="n">
-        <v>185.2523026633164</v>
+        <v>127.400205073642</v>
       </c>
       <c r="K44" t="n">
-        <v>360.923877487437</v>
+        <v>303.0717798977627</v>
       </c>
       <c r="L44" t="n">
-        <v>578.8599999999998</v>
+        <v>521.0079024103255</v>
       </c>
       <c r="M44" t="n">
-        <v>578.8599999999998</v>
+        <v>1076.397902410326</v>
       </c>
       <c r="N44" t="n">
-        <v>578.8599999999998</v>
+        <v>1327.159243836214</v>
       </c>
       <c r="O44" t="n">
-        <v>1135.24</v>
+        <v>1490.301050093541</v>
       </c>
       <c r="P44" t="n">
-        <v>1691.62</v>
+        <v>1688.61</v>
       </c>
       <c r="Q44" t="n">
-        <v>2248</v>
+        <v>2244</v>
       </c>
       <c r="R44" t="n">
-        <v>2248</v>
+        <v>2244</v>
       </c>
       <c r="S44" t="n">
-        <v>2128.74729509841</v>
+        <v>2124.74729509841</v>
       </c>
       <c r="T44" t="n">
-        <v>1890.798730233762</v>
+        <v>1886.798730233762</v>
       </c>
       <c r="U44" t="n">
-        <v>1583.617216538145</v>
+        <v>1579.617216538145</v>
       </c>
       <c r="V44" t="n">
-        <v>1295.888909298929</v>
+        <v>1291.888909298929</v>
       </c>
       <c r="W44" t="n">
-        <v>999.5520648737293</v>
+        <v>995.5520648737293</v>
       </c>
       <c r="X44" t="n">
-        <v>749.7724351154791</v>
+        <v>745.7724351154791</v>
       </c>
       <c r="Y44" t="n">
-        <v>581.7750283651696</v>
+        <v>577.7750283651696</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>738.5992475572438</v>
+        <v>257.4722663890267</v>
       </c>
       <c r="C45" t="n">
-        <v>722.3367097334869</v>
+        <v>241.2097285652699</v>
       </c>
       <c r="D45" t="n">
-        <v>719.3693492307571</v>
+        <v>238.24236806254</v>
       </c>
       <c r="E45" t="n">
-        <v>373.2359176934715</v>
+        <v>238.24236806254</v>
       </c>
       <c r="F45" t="n">
-        <v>373.2359176934715</v>
+        <v>238.24236806254</v>
       </c>
       <c r="G45" t="n">
-        <v>44.96</v>
+        <v>238.24236806254</v>
       </c>
       <c r="H45" t="n">
-        <v>44.96</v>
+        <v>238.24236806254</v>
       </c>
       <c r="I45" t="n">
-        <v>44.96</v>
+        <v>44.88</v>
       </c>
       <c r="J45" t="n">
-        <v>238.7276497036009</v>
+        <v>238.6476497036008</v>
       </c>
       <c r="K45" t="n">
-        <v>547.2388055149654</v>
+        <v>547.1588055149654</v>
       </c>
       <c r="L45" t="n">
-        <v>979.0274996573354</v>
+        <v>976.7579942888729</v>
       </c>
       <c r="M45" t="n">
-        <v>1252.331891400195</v>
+        <v>1250.062386031732</v>
       </c>
       <c r="N45" t="n">
-        <v>1577.79128421531</v>
+        <v>1575.521778846848</v>
       </c>
       <c r="O45" t="n">
-        <v>1992.640074672614</v>
+        <v>1990.370569304152</v>
       </c>
       <c r="P45" t="n">
-        <v>2246.269505368536</v>
+        <v>2244.000000000073</v>
       </c>
       <c r="Q45" t="n">
-        <v>2246.269505368536</v>
+        <v>2165.409242428215</v>
       </c>
       <c r="R45" t="n">
-        <v>2088.76149590606</v>
+        <v>1659.416384480891</v>
       </c>
       <c r="S45" t="n">
-        <v>1631.488397028141</v>
+        <v>1202.143285602972</v>
       </c>
       <c r="T45" t="n">
-        <v>1573.559770069341</v>
+        <v>1144.214658644172</v>
       </c>
       <c r="U45" t="n">
-        <v>1517.841329678834</v>
+        <v>1088.496218253665</v>
       </c>
       <c r="V45" t="n">
-        <v>1447.628534535884</v>
+        <v>1018.283423110715</v>
       </c>
       <c r="W45" t="n">
-        <v>1359.372834626967</v>
+        <v>776.4729622050354</v>
       </c>
       <c r="X45" t="n">
-        <v>1283.753905894252</v>
+        <v>700.8540334723207</v>
       </c>
       <c r="Y45" t="n">
-        <v>1127.040213866665</v>
+        <v>645.9132326984476</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>800.7669289450542</v>
+        <v>845.9472726401018</v>
       </c>
       <c r="C46" t="n">
-        <v>800.7669289450542</v>
+        <v>917.4992784585376</v>
       </c>
       <c r="D46" t="n">
-        <v>859.6360730700543</v>
+        <v>976.3684225835376</v>
       </c>
       <c r="E46" t="n">
-        <v>923.0149772814673</v>
+        <v>976.3684225835376</v>
       </c>
       <c r="F46" t="n">
-        <v>992.9259498734027</v>
+        <v>976.3684225835376</v>
       </c>
       <c r="G46" t="n">
-        <v>1092.501996088157</v>
+        <v>976.3684225835376</v>
       </c>
       <c r="H46" t="n">
-        <v>1092.501996088157</v>
+        <v>1096.942751021624</v>
       </c>
       <c r="I46" t="n">
-        <v>1277.814337975059</v>
+        <v>1096.942751021624</v>
       </c>
       <c r="J46" t="n">
-        <v>1286.695337807839</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="K46" t="n">
-        <v>1414.582122564379</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="L46" t="n">
-        <v>1428.919800524243</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="M46" t="n">
-        <v>1350.592142045098</v>
+        <v>1350.512142045098</v>
       </c>
       <c r="N46" t="n">
-        <v>1218.844525029487</v>
+        <v>1218.764525029487</v>
       </c>
       <c r="O46" t="n">
-        <v>1009.753228311157</v>
+        <v>1009.673228311158</v>
       </c>
       <c r="P46" t="n">
-        <v>740.2908382296055</v>
+        <v>740.2108382296055</v>
       </c>
       <c r="Q46" t="n">
-        <v>408.5309731532438</v>
+        <v>408.4509731532439</v>
       </c>
       <c r="R46" t="n">
-        <v>51.49391723586987</v>
+        <v>51.41391723586987</v>
       </c>
       <c r="S46" t="n">
-        <v>44.96</v>
+        <v>44.88</v>
       </c>
       <c r="T46" t="n">
-        <v>181.2325496506081</v>
+        <v>181.1525496506081</v>
       </c>
       <c r="U46" t="n">
-        <v>373.3675321249603</v>
+        <v>373.2875321249604</v>
       </c>
       <c r="V46" t="n">
-        <v>472.4785813158589</v>
+        <v>517.6589250109064</v>
       </c>
       <c r="W46" t="n">
-        <v>589.9194995755363</v>
+        <v>635.0998432705838</v>
       </c>
       <c r="X46" t="n">
-        <v>686.5002905997299</v>
+        <v>731.6806342947774</v>
       </c>
       <c r="Y46" t="n">
-        <v>743.4595912787621</v>
+        <v>788.6399349738097</v>
       </c>
     </row>
   </sheetData>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>181.5167089435054</v>
       </c>
       <c r="M2" t="n">
-        <v>472.2608914614128</v>
+        <v>845.5549969890515</v>
       </c>
       <c r="N2" t="n">
-        <v>404.0826666125488</v>
+        <v>777.3653500296348</v>
       </c>
       <c r="O2" t="n">
-        <v>295.3388991664989</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P2" t="n">
-        <v>315.3213213472141</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>502.5418702571336</v>
+        <v>502.1077446289935</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>374.2405037325275</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>181.5167089435054</v>
       </c>
       <c r="M5" t="n">
-        <v>472.2608914614128</v>
+        <v>845.5549969890515</v>
       </c>
       <c r="N5" t="n">
-        <v>639.5838718235262</v>
+        <v>777.3653500296348</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.5418702571336</v>
+        <v>502.1077446289935</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>248.2907843203893</v>
+        <v>373.8993027275029</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>309.2909949748744</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>846.2608914614127</v>
+        <v>653.172403205054</v>
       </c>
       <c r="N8" t="n">
-        <v>778.0826666125488</v>
+        <v>777.3653500296348</v>
       </c>
       <c r="O8" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>128.5418702571336</v>
+        <v>502.1077446289935</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,16 +8678,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>50.76301021994982</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>948.3167457327697</v>
+        <v>347.1201599931231</v>
       </c>
       <c r="N11" t="n">
-        <v>228.3401037984784</v>
+        <v>876.3401037984806</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8912,7 +8912,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>425.7387287130186</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -8921,10 +8921,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>948.3167457327697</v>
+        <v>940.7911419000347</v>
       </c>
       <c r="N14" t="n">
-        <v>877.3401037984784</v>
+        <v>876.3401037984811</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -9149,22 +9149,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>161.6659294906854</v>
+        <v>470.5539648241212</v>
       </c>
       <c r="L17" t="n">
-        <v>428.8625025125628</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>299.3167457327696</v>
+        <v>947.31674573277</v>
       </c>
       <c r="N17" t="n">
-        <v>877.3401037984784</v>
+        <v>399.2605351416247</v>
       </c>
       <c r="O17" t="n">
-        <v>484.2102967097708</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -9386,22 +9386,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>428.8625025125627</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>948.3167457327697</v>
+        <v>347.1201599931248</v>
       </c>
       <c r="N20" t="n">
-        <v>228.3401037984784</v>
+        <v>876.3401037984788</v>
       </c>
       <c r="O20" t="n">
-        <v>52.20524429354381</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -9623,25 +9623,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>197.1882968130411</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>423.7791327534237</v>
       </c>
       <c r="L23" t="n">
-        <v>428.8625025125628</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>948.3167457327697</v>
+        <v>947.31674573277</v>
       </c>
       <c r="N23" t="n">
-        <v>228.3401037984784</v>
+        <v>876.3401037984788</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>448.6879293874151</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>22.18109136266131</v>
@@ -9866,10 +9866,10 @@
         <v>471.5539648241206</v>
       </c>
       <c r="L26" t="n">
-        <v>373.1920979153265</v>
+        <v>428.8625025125627</v>
       </c>
       <c r="M26" t="n">
-        <v>299.3167457327696</v>
+        <v>692.3342705229481</v>
       </c>
       <c r="N26" t="n">
         <v>228.3401037984784</v>
@@ -9878,7 +9878,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>448.6879293874151</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>22.18109136266131</v>
@@ -10097,28 +10097,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>471.5539648241206</v>
       </c>
       <c r="L29" t="n">
-        <v>337.6697305929708</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>299.3167457327696</v>
+        <v>948.3167457327695</v>
       </c>
       <c r="N29" t="n">
-        <v>228.3401037984784</v>
+        <v>237.8538857804645</v>
       </c>
       <c r="O29" t="n">
-        <v>484.2102967097708</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10340,19 +10340,19 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>197.1695207089205</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>299.3167457327696</v>
+        <v>948.3167457327695</v>
       </c>
       <c r="N32" t="n">
-        <v>228.3401037984784</v>
+        <v>709.4078506045851</v>
       </c>
       <c r="O32" t="n">
-        <v>484.2102967097708</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>448.6879293874151</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10580,16 +10580,16 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>324.577959987368</v>
+        <v>322.6183640277723</v>
       </c>
       <c r="N35" t="n">
-        <v>790.3401037984784</v>
+        <v>789.3401037984784</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>361.6879293874151</v>
+        <v>360.6879293874151</v>
       </c>
       <c r="Q35" t="n">
         <v>22.18109136266131</v>
@@ -10656,7 +10656,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>388.0893364597981</v>
+        <v>385.8777148754926</v>
       </c>
       <c r="M36" t="n">
         <v>471.6948204301074</v>
@@ -10811,25 +10811,25 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>58.35565413098425</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>299.3167457327696</v>
+        <v>860.3167457327697</v>
       </c>
       <c r="N38" t="n">
-        <v>228.3401037984784</v>
+        <v>681.9464586796378</v>
       </c>
       <c r="O38" t="n">
-        <v>397.2102967097708</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>361.6879293874151</v>
+        <v>360.6879293874151</v>
       </c>
       <c r="Q38" t="n">
-        <v>584.1810913626613</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10893,7 +10893,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>388.0893364597981</v>
+        <v>385.8777148754853</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
@@ -11051,13 +11051,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>341.8625025125629</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>861.3167457327697</v>
+        <v>860.3167457327697</v>
       </c>
       <c r="N41" t="n">
-        <v>703.731481514086</v>
+        <v>789.3401037984784</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>22.18109136266131</v>
+        <v>275.4753756312358</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11136,7 +11136,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N42" t="n">
-        <v>485.4085271713503</v>
+        <v>483.1969055870447</v>
       </c>
       <c r="O42" t="n">
         <v>382.6817988009037</v>
@@ -11282,7 +11282,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>58.35565413098423</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -11291,19 +11291,19 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>299.3167457327696</v>
+        <v>860.3167457327697</v>
       </c>
       <c r="N44" t="n">
-        <v>228.3401037984784</v>
+        <v>481.634388067053</v>
       </c>
       <c r="O44" t="n">
-        <v>397.2102967097708</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>361.6879293874151</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>584.1810913626613</v>
+        <v>583.1810913626613</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11367,7 +11367,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>388.0893364597981</v>
+        <v>385.8777148754926</v>
       </c>
       <c r="M45" t="n">
         <v>471.6948204301074</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.831690603168681e-13</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -23238,7 +23238,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2.956056855789868</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -23478,7 +23478,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2.956056855773028</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23712,7 +23712,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2.956056855789868</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -23952,7 +23952,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2.956056855764643</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>2.956056855789797</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7048568557918031</v>
+        <v>4.585656855791804</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -25407,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.7048568557913342</v>
+        <v>4.585656855726114</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7048568557917179</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -25644,7 +25644,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>4.585656855791399</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -25830,7 +25830,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7048568557917179</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -25845,7 +25845,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>4.585656855791843</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>853738.030650863</v>
+        <v>853628.188650863</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1609364.254850419</v>
+        <v>1609254.412850419</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2364990.479049976</v>
+        <v>2364880.637049976</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3119708.079916201</v>
+        <v>3119472.343489253</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3875334.304115758</v>
+        <v>3874957.386413379</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4630960.528315314</v>
+        <v>4630442.429337503</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5386586.752514868</v>
+        <v>5385927.472261625</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6142212.976714422</v>
+        <v>6141412.515185747</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6897839.200913976</v>
+        <v>6897133.294536816</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7653465.42511353</v>
+        <v>7652759.51873637</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8409091.649313089</v>
+        <v>8408385.742935928</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9156457.9113674</v>
+        <v>9155443.971004171</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9912050.47160353</v>
+        <v>9910851.184232304</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10667643.03183966</v>
+        <v>10666258.39746043</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11423235.59207579</v>
+        <v>11421665.61068856</v>
       </c>
     </row>
   </sheetData>
@@ -26269,28 +26269,28 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>1448283.596382485</v>
+      </c>
+      <c r="C2" t="n">
         <v>1448283.596382484</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>1448283.596382485</v>
       </c>
-      <c r="D2" t="n">
-        <v>1448283.596382484</v>
-      </c>
       <c r="E2" t="n">
-        <v>1448283.596382484</v>
+        <v>1448012.998937905</v>
       </c>
       <c r="F2" t="n">
-        <v>1448283.596382484</v>
+        <v>1448012.998937906</v>
       </c>
       <c r="G2" t="n">
-        <v>1448283.596382484</v>
+        <v>1448012.998937905</v>
       </c>
       <c r="H2" t="n">
-        <v>1448283.596382484</v>
+        <v>1448012.998937908</v>
       </c>
       <c r="I2" t="n">
-        <v>1448283.596382484</v>
+        <v>1448012.998937905</v>
       </c>
       <c r="J2" t="n">
         <v>1448283.596382484</v>
@@ -26302,16 +26302,16 @@
         <v>1448283.596382484</v>
       </c>
       <c r="M2" t="n">
-        <v>1448219.073785906</v>
+        <v>1447863.825353905</v>
       </c>
       <c r="N2" t="n">
-        <v>1448219.073785905</v>
+        <v>1447863.825353912</v>
       </c>
       <c r="O2" t="n">
-        <v>1448219.073785905</v>
+        <v>1447863.825353905</v>
       </c>
       <c r="P2" t="n">
-        <v>1448219.073785905</v>
+        <v>1447863.825353905</v>
       </c>
     </row>
     <row r="3">
@@ -26321,7 +26321,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231098</v>
+        <v>232073.0000000002</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26330,7 +26330,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>592475</v>
+        <v>591148</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388448</v>
+        <v>388800</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>85376</v>
+        <v>84672</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101187</v>
+        <v>601967.7658514546</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.25402263</v>
+        <v>599959.4017938484</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.606606806</v>
+        <v>597948.3132650449</v>
       </c>
       <c r="E4" t="n">
-        <v>514005.3727838712</v>
+        <v>513751.7523916514</v>
       </c>
       <c r="F4" t="n">
-        <v>512320.9448683569</v>
+        <v>512067.154639688</v>
       </c>
       <c r="G4" t="n">
-        <v>510634.1925055168</v>
+        <v>510380.2322060294</v>
       </c>
       <c r="H4" t="n">
-        <v>508945.09902665</v>
+        <v>508690.9684202975</v>
       </c>
       <c r="I4" t="n">
-        <v>507253.6475458712</v>
+        <v>506999.3463948999</v>
       </c>
       <c r="J4" t="n">
-        <v>505559.8209559914</v>
+        <v>505362.3521738977</v>
       </c>
       <c r="K4" t="n">
-        <v>503863.6019243027</v>
+        <v>503666.133142209</v>
       </c>
       <c r="L4" t="n">
-        <v>502164.9728882493</v>
+        <v>501967.5041061557</v>
       </c>
       <c r="M4" t="n">
-        <v>506566.2673210928</v>
+        <v>506308.908453467</v>
       </c>
       <c r="N4" t="n">
-        <v>504800.3868513845</v>
+        <v>504542.8135297524</v>
       </c>
       <c r="O4" t="n">
-        <v>503031.9520361846</v>
+        <v>502774.1639503327</v>
       </c>
       <c r="P4" t="n">
-        <v>501260.9436696268</v>
+        <v>501002.9405070178</v>
       </c>
     </row>
     <row r="5">
@@ -26425,28 +26425,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.20000000003</v>
       </c>
       <c r="C5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.20000000003</v>
       </c>
       <c r="D5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.20000000003</v>
       </c>
       <c r="E5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.14900000003</v>
       </c>
       <c r="F5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.14900000003</v>
       </c>
       <c r="G5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.14900000003</v>
       </c>
       <c r="H5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.14900000003</v>
       </c>
       <c r="I5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.14900000003</v>
       </c>
       <c r="J5" t="n">
         <v>74009.94899999999</v>
@@ -26458,16 +26458,16 @@
         <v>74009.94899999999</v>
       </c>
       <c r="M5" t="n">
-        <v>70738.005</v>
+        <v>70677.20499999999</v>
       </c>
       <c r="N5" t="n">
-        <v>70738.005</v>
+        <v>70677.20499999999</v>
       </c>
       <c r="O5" t="n">
-        <v>70738.005</v>
+        <v>70677.20499999999</v>
       </c>
       <c r="P5" t="n">
-        <v>70738.005</v>
+        <v>70677.20499999999</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>556176.0201723656</v>
+        <v>555630.6305310301</v>
       </c>
       <c r="C6" t="n">
-        <v>789282.9423598549</v>
+        <v>789711.9945886356</v>
       </c>
       <c r="D6" t="n">
-        <v>791294.589775678</v>
+        <v>791723.08311744</v>
       </c>
       <c r="E6" t="n">
-        <v>267793.2745986131</v>
+        <v>269164.0975462534</v>
       </c>
       <c r="F6" t="n">
-        <v>861952.7025141269</v>
+        <v>861996.6952982177</v>
       </c>
       <c r="G6" t="n">
-        <v>863639.454876967</v>
+        <v>863683.6177318755</v>
       </c>
       <c r="H6" t="n">
-        <v>865328.5483558343</v>
+        <v>865372.8815176103</v>
       </c>
       <c r="I6" t="n">
-        <v>867019.9998366128</v>
+        <v>867064.5035430046</v>
       </c>
       <c r="J6" t="n">
-        <v>480265.8264264929</v>
+        <v>480111.2952085866</v>
       </c>
       <c r="K6" t="n">
-        <v>870410.0454581815</v>
+        <v>870607.5142402749</v>
       </c>
       <c r="L6" t="n">
-        <v>872108.6744942347</v>
+        <v>872306.1432763285</v>
       </c>
       <c r="M6" t="n">
-        <v>785538.8014648132</v>
+        <v>786205.7119004383</v>
       </c>
       <c r="N6" t="n">
-        <v>872680.681934521</v>
+        <v>872643.8068241595</v>
       </c>
       <c r="O6" t="n">
-        <v>617649.1167497209</v>
+        <v>617612.4564035727</v>
       </c>
       <c r="P6" t="n">
-        <v>876220.1251162783</v>
+        <v>876183.6798468876</v>
       </c>
     </row>
   </sheetData>
@@ -26807,13 +26807,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" t="n">
         <v>347</v>
@@ -26859,28 +26859,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="C4" t="n">
-        <v>374</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="D4" t="n">
-        <v>374</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="E4" t="n">
-        <v>649</v>
+        <v>648.0000000000005</v>
       </c>
       <c r="F4" t="n">
-        <v>649</v>
+        <v>648.0000000000005</v>
       </c>
       <c r="G4" t="n">
-        <v>649</v>
+        <v>648.0000000000005</v>
       </c>
       <c r="H4" t="n">
-        <v>649</v>
+        <v>648.0000000000005</v>
       </c>
       <c r="I4" t="n">
-        <v>649</v>
+        <v>648.0000000000005</v>
       </c>
       <c r="J4" t="n">
         <v>649</v>
@@ -26892,16 +26892,16 @@
         <v>649</v>
       </c>
       <c r="M4" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="N4" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="O4" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="P4" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>
@@ -26987,7 +26987,7 @@
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -26999,10 +26999,10 @@
         <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>24</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27033,7 +27033,7 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27085,7 +27085,7 @@
         <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -27100,7 +27100,7 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27109,7 +27109,7 @@
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="N4" t="n">
         <v>-0</v>
@@ -27317,7 +27317,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -27326,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27445,7 +27445,7 @@
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>400</v>
+        <v>398.0465935392065</v>
       </c>
       <c r="G2" t="n">
         <v>400</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>132.4740095032998</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27521,19 +27521,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>157.1970077340415</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,13 +27557,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>400</v>
+        <v>284.0868824730753</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>25.39139276613383</v>
       </c>
     </row>
     <row r="4">
@@ -27591,31 +27591,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
         <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>350.2141662217153</v>
+        <v>244.858135136612</v>
       </c>
       <c r="H4" t="n">
-        <v>227.1357818393235</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I4" t="n">
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>396.2647849014816</v>
+        <v>396.1372930982034</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
@@ -27645,13 +27645,13 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>209.2386648669134</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>347.6483414931789</v>
       </c>
       <c r="W4" t="n">
         <v>226.3728098387097</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>132.4740095033003</v>
+        <v>132.1643059857103</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27755,7 +27755,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>120.3562017409445</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27764,13 +27764,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27803,22 +27803,22 @@
         <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>30.47344446279683</v>
+        <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>26.19578428848814</v>
       </c>
       <c r="V6" t="n">
-        <v>400</v>
+        <v>285.7214545851382</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>58.373142909828</v>
       </c>
       <c r="X6" t="n">
-        <v>400</v>
+        <v>45.86273944538704</v>
       </c>
       <c r="Y6" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -27834,25 +27834,25 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>342.0400961869582</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
         <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>22.26478490148153</v>
+        <v>396.1372930982034</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
@@ -27879,19 +27879,19 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T7" t="n">
-        <v>394.7415018413055</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>132.4740095033003</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,10 +27955,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>398.0465935392065</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27986,28 +27986,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>150.3394582498843</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5201396486123</v>
+        <v>185.0793619393663</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,10 +28031,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
-        <v>159.6519859716246</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28068,34 +28068,34 @@
         <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
         <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I10" t="n">
-        <v>221.2248850766712</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J10" t="n">
-        <v>22.26478490148153</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,19 +28116,19 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T10" t="n">
-        <v>209.2386648669134</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U10" t="n">
         <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>367.9755650525142</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
@@ -28165,7 +28165,7 @@
         <v>321</v>
       </c>
       <c r="I11" t="n">
-        <v>95.37664769425496</v>
+        <v>96.3013908384635</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28229,13 +28229,13 @@
         <v>321</v>
       </c>
       <c r="D12" t="n">
-        <v>8.269477602770905</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>321</v>
@@ -28244,7 +28244,7 @@
         <v>321</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28271,10 +28271,10 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T12" t="n">
         <v>321</v>
@@ -28286,7 +28286,7 @@
         <v>321</v>
       </c>
       <c r="W12" t="n">
-        <v>321</v>
+        <v>137.8407332208565</v>
       </c>
       <c r="X12" t="n">
         <v>321</v>
@@ -28326,7 +28326,7 @@
         <v>321</v>
       </c>
       <c r="J13" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="K13" t="n">
         <v>321</v>
@@ -28362,7 +28362,7 @@
         <v>321</v>
       </c>
       <c r="V13" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
       <c r="W13" t="n">
         <v>321</v>
@@ -28402,7 +28402,7 @@
         <v>321</v>
       </c>
       <c r="I14" t="n">
-        <v>95.37664769425513</v>
+        <v>96.3013908384635</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>163.2515083760331</v>
+        <v>163.2515083760501</v>
       </c>
       <c r="S14" t="n">
         <v>321</v>
@@ -28469,10 +28469,10 @@
         <v>321</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G15" t="n">
         <v>321</v>
@@ -28520,16 +28520,16 @@
         <v>321</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="W15" t="n">
-        <v>137.8407332208563</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -28551,7 +28551,7 @@
         <v>321</v>
       </c>
       <c r="F16" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="G16" t="n">
         <v>321</v>
@@ -28602,7 +28602,7 @@
         <v>321</v>
       </c>
       <c r="W16" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="X16" t="n">
         <v>321</v>
@@ -28639,7 +28639,7 @@
         <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>95.37664769425496</v>
+        <v>96.3013908384635</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28700,25 +28700,25 @@
         <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D18" t="n">
         <v>321</v>
       </c>
       <c r="E18" t="n">
-        <v>8.269477602771019</v>
+        <v>321</v>
       </c>
       <c r="F18" t="n">
         <v>321</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H18" t="n">
         <v>321</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28757,16 +28757,16 @@
         <v>321</v>
       </c>
       <c r="V18" t="n">
-        <v>321</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="W18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -28800,7 +28800,7 @@
         <v>321</v>
       </c>
       <c r="J19" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="K19" t="n">
         <v>321</v>
@@ -28833,7 +28833,7 @@
         <v>321</v>
       </c>
       <c r="U19" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="V19" t="n">
         <v>321</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>162.3267652318248</v>
+        <v>163.2515083760589</v>
       </c>
       <c r="S20" t="n">
         <v>321</v>
@@ -28937,16 +28937,16 @@
         <v>321</v>
       </c>
       <c r="C21" t="n">
-        <v>321</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="D21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
@@ -28994,16 +28994,16 @@
         <v>321</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X21" t="n">
-        <v>137.8407332208564</v>
+        <v>321</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="22">
@@ -29037,7 +29037,7 @@
         <v>321</v>
       </c>
       <c r="J22" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="K22" t="n">
         <v>321</v>
@@ -29070,7 +29070,7 @@
         <v>321</v>
       </c>
       <c r="U22" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="V22" t="n">
         <v>321</v>
@@ -29113,7 +29113,7 @@
         <v>321</v>
       </c>
       <c r="I23" t="n">
-        <v>95.37664769425513</v>
+        <v>96.3013908384635</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29225,13 +29225,13 @@
         <v>321</v>
       </c>
       <c r="T24" t="n">
-        <v>137.8407332208565</v>
+        <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V24" t="n">
-        <v>321</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -29240,7 +29240,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -29274,7 +29274,7 @@
         <v>321</v>
       </c>
       <c r="J25" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="K25" t="n">
         <v>321</v>
@@ -29313,7 +29313,7 @@
         <v>321</v>
       </c>
       <c r="W25" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="X25" t="n">
         <v>321</v>
@@ -29350,7 +29350,7 @@
         <v>321</v>
       </c>
       <c r="I26" t="n">
-        <v>95.37664769425513</v>
+        <v>95.37664769425514</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29411,25 +29411,25 @@
         <v>321</v>
       </c>
       <c r="C27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>321</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>86.07432759891067</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R27" t="n">
         <v>321</v>
@@ -29474,7 +29474,7 @@
         <v>321</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y27" t="n">
         <v>321</v>
@@ -29514,7 +29514,7 @@
         <v>321</v>
       </c>
       <c r="K28" t="n">
-        <v>321</v>
+        <v>315.8198010595346</v>
       </c>
       <c r="L28" t="n">
         <v>321</v>
@@ -29544,7 +29544,7 @@
         <v>321</v>
       </c>
       <c r="U28" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="V28" t="n">
         <v>321</v>
@@ -29584,7 +29584,7 @@
         <v>321</v>
       </c>
       <c r="H29" t="n">
-        <v>321</v>
+        <v>320.0752568557915</v>
       </c>
       <c r="I29" t="n">
         <v>96.3013908384635</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>162.3267652318248</v>
+        <v>163.2515083760331</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29645,13 +29645,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>321</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E30" t="n">
         <v>321</v>
@@ -29663,7 +29663,7 @@
         <v>321</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I30" t="n">
         <v>191.4287443819146</v>
@@ -29705,10 +29705,10 @@
         <v>321</v>
       </c>
       <c r="V30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>137.8407332208563</v>
+        <v>137.8407332208565</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -29730,7 +29730,7 @@
         <v>321</v>
       </c>
       <c r="D31" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="E31" t="n">
         <v>321</v>
@@ -29748,7 +29748,7 @@
         <v>321</v>
       </c>
       <c r="J31" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="K31" t="n">
         <v>321</v>
@@ -29821,7 +29821,7 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>320.0752568557916</v>
+        <v>321</v>
       </c>
       <c r="I32" t="n">
         <v>96.3013908384635</v>
@@ -29860,7 +29860,7 @@
         <v>321</v>
       </c>
       <c r="U32" t="n">
-        <v>321</v>
+        <v>320.0752568557916</v>
       </c>
       <c r="V32" t="n">
         <v>321</v>
@@ -29882,16 +29882,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>321</v>
+        <v>137.8407332208565</v>
       </c>
       <c r="F33" t="n">
         <v>321</v>
@@ -29930,13 +29930,13 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S33" t="n">
-        <v>137.8407332208566</v>
+        <v>321</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U33" t="n">
         <v>321</v>
@@ -29945,7 +29945,7 @@
         <v>321</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X33" t="n">
         <v>321</v>
@@ -29985,7 +29985,7 @@
         <v>321</v>
       </c>
       <c r="J34" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="K34" t="n">
         <v>321</v>
@@ -30030,7 +30030,7 @@
         <v>321</v>
       </c>
       <c r="Y34" t="n">
-        <v>315.8198010595348</v>
+        <v>321</v>
       </c>
     </row>
     <row r="35">
@@ -30140,7 +30140,7 @@
         <v>324.959653224157</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30164,28 +30164,28 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>77.80484999613995</v>
+        <v>1.552042231291026</v>
       </c>
       <c r="R36" t="n">
         <v>345</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="T36" t="n">
         <v>345</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="V36" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>113.008326302288</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -30201,13 +30201,13 @@
         <v>345</v>
       </c>
       <c r="C37" t="n">
-        <v>294.4265194262327</v>
+        <v>345</v>
       </c>
       <c r="D37" t="n">
         <v>345</v>
       </c>
       <c r="E37" t="n">
-        <v>280.9809048369565</v>
+        <v>345</v>
       </c>
       <c r="F37" t="n">
         <v>345</v>
@@ -30225,7 +30225,7 @@
         <v>345</v>
       </c>
       <c r="K37" t="n">
-        <v>215.821429538848</v>
+        <v>345</v>
       </c>
       <c r="L37" t="n">
         <v>345</v>
@@ -30252,22 +30252,22 @@
         <v>345</v>
       </c>
       <c r="T37" t="n">
-        <v>207.3509599488807</v>
+        <v>218.7480966347538</v>
       </c>
       <c r="U37" t="n">
-        <v>345</v>
+        <v>150.9242601269169</v>
       </c>
       <c r="V37" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>345</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X37" t="n">
         <v>345</v>
       </c>
       <c r="Y37" t="n">
-        <v>287.4653528494624</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38">
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>163.2515083760331</v>
+        <v>163.2515083760998</v>
       </c>
       <c r="S38" t="n">
         <v>345</v>
@@ -30377,7 +30377,7 @@
         <v>324.959653224157</v>
       </c>
       <c r="I39" t="n">
-        <v>191.4287443819146</v>
+        <v>190.6528838351254</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>345</v>
@@ -30416,16 +30416,16 @@
         <v>345</v>
       </c>
       <c r="V39" t="n">
-        <v>264.2516791422858</v>
+        <v>345</v>
       </c>
       <c r="W39" t="n">
         <v>345</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="Y39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -30435,19 +30435,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>287.1138003370787</v>
+        <v>345</v>
       </c>
       <c r="C40" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D40" t="n">
-        <v>285.5362180555555</v>
+        <v>345</v>
       </c>
       <c r="E40" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F40" t="n">
         <v>345</v>
-      </c>
-      <c r="F40" t="n">
-        <v>274.3828559677419</v>
       </c>
       <c r="G40" t="n">
         <v>345</v>
@@ -30492,10 +30492,10 @@
         <v>345</v>
       </c>
       <c r="U40" t="n">
-        <v>345</v>
+        <v>316.0572069970995</v>
       </c>
       <c r="V40" t="n">
-        <v>236.6409005393585</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W40" t="n">
         <v>226.3728098387097</v>
@@ -30504,7 +30504,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y40" t="n">
-        <v>345</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="41">
@@ -30593,7 +30593,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>345</v>
@@ -30602,19 +30602,19 @@
         <v>345</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>324.9931585165368</v>
       </c>
       <c r="H42" t="n">
         <v>324.959653224157</v>
       </c>
       <c r="I42" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30638,7 +30638,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -30647,13 +30647,13 @@
         <v>345</v>
       </c>
       <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
         <v>345</v>
       </c>
-      <c r="U42" t="n">
-        <v>238.8810799966996</v>
-      </c>
       <c r="V42" t="n">
-        <v>345</v>
+        <v>192.9807866132052</v>
       </c>
       <c r="W42" t="n">
         <v>345</v>
@@ -30684,7 +30684,7 @@
         <v>345</v>
       </c>
       <c r="F43" t="n">
-        <v>274.3828559677419</v>
+        <v>345</v>
       </c>
       <c r="G43" t="n">
         <v>345</v>
@@ -30693,16 +30693,16 @@
         <v>223.2077490524383</v>
       </c>
       <c r="I43" t="n">
+        <v>157.815816275856</v>
+      </c>
+      <c r="J43" t="n">
         <v>345</v>
-      </c>
-      <c r="J43" t="n">
-        <v>306.4574565787184</v>
       </c>
       <c r="K43" t="n">
         <v>345</v>
       </c>
       <c r="L43" t="n">
-        <v>345</v>
+        <v>330.5174970102382</v>
       </c>
       <c r="M43" t="n">
         <v>345</v>
@@ -30726,19 +30726,19 @@
         <v>345</v>
       </c>
       <c r="T43" t="n">
-        <v>207.3509599488807</v>
+        <v>345</v>
       </c>
       <c r="U43" t="n">
+        <v>229.504104261848</v>
+      </c>
+      <c r="V43" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W43" t="n">
         <v>345</v>
       </c>
-      <c r="V43" t="n">
+      <c r="X43" t="n">
         <v>345</v>
-      </c>
-      <c r="W43" t="n">
-        <v>226.3728098387097</v>
-      </c>
-      <c r="X43" t="n">
-        <v>247.4436454301076</v>
       </c>
       <c r="Y43" t="n">
         <v>345</v>
@@ -30839,19 +30839,19 @@
         <v>345</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>324.9931585165368</v>
       </c>
       <c r="H45" t="n">
         <v>324.959653224157</v>
       </c>
       <c r="I45" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30875,10 +30875,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -30893,13 +30893,13 @@
         <v>345</v>
       </c>
       <c r="W45" t="n">
-        <v>345</v>
+        <v>192.9807866132052</v>
       </c>
       <c r="X45" t="n">
         <v>345</v>
       </c>
       <c r="Y45" t="n">
-        <v>244.2448376588227</v>
+        <v>345</v>
       </c>
     </row>
     <row r="46">
@@ -30912,34 +30912,34 @@
         <v>345</v>
       </c>
       <c r="C46" t="n">
-        <v>272.7252466480447</v>
+        <v>345</v>
       </c>
       <c r="D46" t="n">
         <v>345</v>
       </c>
       <c r="E46" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F46" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G46" t="n">
+        <v>244.418135136612</v>
+      </c>
+      <c r="H46" t="n">
         <v>345</v>
       </c>
-      <c r="F46" t="n">
-        <v>345</v>
-      </c>
-      <c r="G46" t="n">
-        <v>345</v>
-      </c>
-      <c r="H46" t="n">
-        <v>223.2077490524383</v>
-      </c>
       <c r="I46" t="n">
-        <v>345</v>
+        <v>157.815816275856</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>326.2788380503437</v>
       </c>
       <c r="K46" t="n">
-        <v>345</v>
+        <v>215.821429538848</v>
       </c>
       <c r="L46" t="n">
-        <v>345</v>
+        <v>330.5174970102382</v>
       </c>
       <c r="M46" t="n">
         <v>345</v>
@@ -30969,7 +30969,7 @@
         <v>345</v>
       </c>
       <c r="V46" t="n">
-        <v>299.2824811161137</v>
+        <v>345</v>
       </c>
       <c r="W46" t="n">
         <v>345</v>
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H2" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I2" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J2" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K2" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M2" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N2" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O2" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P2" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R2" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S2" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T2" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H3" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I3" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K3" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L3" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M3" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O3" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P3" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R3" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S3" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H4" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I4" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J4" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K4" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L4" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M4" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N4" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O4" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P4" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R4" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S4" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H5" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I5" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J5" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K5" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M5" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N5" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O5" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P5" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R5" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S5" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T5" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H6" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I6" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J6" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K6" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L6" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M6" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O6" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P6" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R6" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S6" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H7" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I7" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J7" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K7" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L7" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M7" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N7" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O7" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P7" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R7" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S7" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31565,49 +31565,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H8" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I8" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J8" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K8" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M8" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N8" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O8" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P8" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R8" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S8" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T8" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31644,49 +31644,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H9" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I9" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J9" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K9" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L9" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M9" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O9" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P9" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R9" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S9" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,49 +31723,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H10" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I10" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J10" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K10" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L10" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M10" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N10" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O10" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P10" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R10" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S10" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T10" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K2" t="n">
-        <v>374</v>
+        <v>52.6713015075377</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>246.8601159786813</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="O2" t="n">
-        <v>294.1798838637633</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>374</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
-        <v>374</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K3" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L3" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M3" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O3" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P3" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34877,37 +34877,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>105.3542278064148</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>228.8979542159473</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="K4" t="n">
-        <v>132.8490622644307</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L4" t="n">
-        <v>3.798404629106074</v>
+        <v>4.066502989761812</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,16 +34928,16 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.83199570698065</v>
+        <v>40.86342193648883</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>148.4780312769627</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>374</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K5" t="n">
-        <v>373.9999999999999</v>
+        <v>52.6713015075377</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>246.8601159786813</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="N5" t="n">
-        <v>235.5012052109774</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q5" t="n">
-        <v>374</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K6" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L6" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M6" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O6" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P6" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35120,31 +35120,31 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>56.50387813140271</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>155.1400615846995</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I7" t="n">
-        <v>228.8979542159473</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="K7" t="n">
-        <v>132.8490622644307</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L7" t="n">
-        <v>3.798404629106074</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,19 +35165,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>185.502836974392</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -35217,28 +35217,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>248.0502805878618</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="K8" t="n">
-        <v>52.15992964824119</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>374</v>
+        <v>65.34340703517586</v>
       </c>
       <c r="M8" t="n">
-        <v>374</v>
+        <v>181.617406216003</v>
       </c>
       <c r="N8" t="n">
-        <v>374</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>374.0000000000005</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35296,25 +35296,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K9" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L9" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M9" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O9" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P9" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35354,34 +35354,34 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>155.1400615846995</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>50.1228392926185</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,19 +35402,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0516415124273</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>168.805254836298</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
@@ -35457,16 +35457,16 @@
         <v>513.658479084785</v>
       </c>
       <c r="K11" t="n">
-        <v>228.2090453958292</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L11" t="n">
-        <v>220.1374974874373</v>
+        <v>220.1374974874371</v>
       </c>
       <c r="M11" t="n">
-        <v>649</v>
+        <v>47.80341426035353</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>648.0000000000022</v>
       </c>
       <c r="O11" t="n">
         <v>164.7897032902292</v>
@@ -35612,7 +35612,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J13" t="n">
-        <v>324.7905079613318</v>
+        <v>329.9707069017971</v>
       </c>
       <c r="K13" t="n">
         <v>105.178570461152</v>
@@ -35648,7 +35648,7 @@
         <v>170.0757398730831</v>
       </c>
       <c r="V13" t="n">
-        <v>121.8296897837838</v>
+        <v>116.6494908433186</v>
       </c>
       <c r="W13" t="n">
         <v>94.62719016129032</v>
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>509.0924712116469</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K14" t="n">
         <v>177.4460351758794</v>
       </c>
       <c r="L14" t="n">
-        <v>220.1374974874373</v>
+        <v>220.1374974874371</v>
       </c>
       <c r="M14" t="n">
-        <v>649</v>
+        <v>641.4743961672651</v>
       </c>
       <c r="N14" t="n">
-        <v>649</v>
+        <v>648.0000000000028</v>
       </c>
       <c r="O14" t="n">
         <v>164.7897032902292</v>
@@ -35715,7 +35715,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.699560806343351e-11</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -35837,7 +35837,7 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F16" t="n">
-        <v>46.61714403225807</v>
+        <v>41.43694509179277</v>
       </c>
       <c r="G16" t="n">
         <v>76.58186486338801</v>
@@ -35888,7 +35888,7 @@
         <v>121.8296897837838</v>
       </c>
       <c r="W16" t="n">
-        <v>89.44699122082505</v>
+        <v>94.62719016129032</v>
       </c>
       <c r="X16" t="n">
         <v>73.55635456989245</v>
@@ -35928,22 +35928,22 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K17" t="n">
-        <v>339.1119646665647</v>
+        <v>648.0000000000006</v>
       </c>
       <c r="L17" t="n">
-        <v>649</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>648.0000000000005</v>
       </c>
       <c r="N17" t="n">
-        <v>649</v>
+        <v>170.9204313431462</v>
       </c>
       <c r="O17" t="n">
-        <v>649</v>
+        <v>164.7897032902292</v>
       </c>
       <c r="P17" t="n">
         <v>200.3120706125849</v>
@@ -36086,7 +36086,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J19" t="n">
-        <v>329.9707069017971</v>
+        <v>324.7905079613318</v>
       </c>
       <c r="K19" t="n">
         <v>105.178570461152</v>
@@ -36119,7 +36119,7 @@
         <v>113.6490400511193</v>
       </c>
       <c r="U19" t="n">
-        <v>164.8955409326178</v>
+        <v>170.0757398730831</v>
       </c>
       <c r="V19" t="n">
         <v>121.8296897837838</v>
@@ -36165,22 +36165,22 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K20" t="n">
         <v>177.4460351758794</v>
       </c>
       <c r="L20" t="n">
-        <v>649</v>
+        <v>220.1374974874371</v>
       </c>
       <c r="M20" t="n">
-        <v>649</v>
+        <v>47.80341426035526</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>648.0000000000005</v>
       </c>
       <c r="O20" t="n">
-        <v>216.994947583773</v>
+        <v>164.7897032902292</v>
       </c>
       <c r="P20" t="n">
         <v>200.3120706125849</v>
@@ -36189,7 +36189,7 @@
         <v>593.6709819069124</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.572308247438585e-11</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -36323,7 +36323,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J22" t="n">
-        <v>329.9707069017971</v>
+        <v>324.7905079613318</v>
       </c>
       <c r="K22" t="n">
         <v>105.178570461152</v>
@@ -36356,7 +36356,7 @@
         <v>113.6490400511193</v>
       </c>
       <c r="U22" t="n">
-        <v>164.8955409326178</v>
+        <v>170.0757398730831</v>
       </c>
       <c r="V22" t="n">
         <v>121.8296897837838</v>
@@ -36402,25 +36402,25 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>280.5420393116693</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K23" t="n">
-        <v>177.4460351758794</v>
+        <v>601.2251679293031</v>
       </c>
       <c r="L23" t="n">
-        <v>649</v>
+        <v>220.1374974874371</v>
       </c>
       <c r="M23" t="n">
-        <v>649</v>
+        <v>648.0000000000005</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>648.0000000000005</v>
       </c>
       <c r="O23" t="n">
         <v>164.7897032902292</v>
       </c>
       <c r="P23" t="n">
-        <v>649</v>
+        <v>200.3120706125849</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36560,7 +36560,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J25" t="n">
-        <v>329.9707069017971</v>
+        <v>324.7905079613318</v>
       </c>
       <c r="K25" t="n">
         <v>105.178570461152</v>
@@ -36599,7 +36599,7 @@
         <v>121.8296897837838</v>
       </c>
       <c r="W25" t="n">
-        <v>89.44699122082505</v>
+        <v>94.62719016129032</v>
       </c>
       <c r="X25" t="n">
         <v>73.55635456989245</v>
@@ -36645,10 +36645,10 @@
         <v>649</v>
       </c>
       <c r="L26" t="n">
-        <v>593.3295954027637</v>
+        <v>649</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>393.0175247901786</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -36657,7 +36657,7 @@
         <v>164.7897032902292</v>
       </c>
       <c r="P26" t="n">
-        <v>649</v>
+        <v>200.3120706125849</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36800,7 +36800,7 @@
         <v>329.9707069017971</v>
       </c>
       <c r="K28" t="n">
-        <v>105.178570461152</v>
+        <v>99.99837152068662</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -36830,7 +36830,7 @@
         <v>113.6490400511193</v>
       </c>
       <c r="U28" t="n">
-        <v>164.8955409326178</v>
+        <v>170.0757398730831</v>
       </c>
       <c r="V28" t="n">
         <v>121.8296897837838</v>
@@ -36876,28 +36876,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K29" t="n">
         <v>649</v>
       </c>
       <c r="L29" t="n">
-        <v>557.8072280804081</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>9.513781981986035</v>
       </c>
       <c r="O29" t="n">
-        <v>649</v>
+        <v>164.7897032902292</v>
       </c>
       <c r="P29" t="n">
         <v>200.3120706125849</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37016,7 +37016,7 @@
         <v>48.27475335195533</v>
       </c>
       <c r="D31" t="n">
-        <v>35.46378194444452</v>
+        <v>30.28358300397924</v>
       </c>
       <c r="E31" t="n">
         <v>40.01909516304346</v>
@@ -37034,7 +37034,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J31" t="n">
-        <v>324.7905079613318</v>
+        <v>329.9707069017971</v>
       </c>
       <c r="K31" t="n">
         <v>105.178570461152</v>
@@ -37119,19 +37119,19 @@
         <v>177.4460351758794</v>
       </c>
       <c r="L32" t="n">
-        <v>417.3070181963577</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>481.0677468061066</v>
       </c>
       <c r="O32" t="n">
-        <v>649</v>
+        <v>164.7897032902292</v>
       </c>
       <c r="P32" t="n">
-        <v>649</v>
+        <v>200.3120706125849</v>
       </c>
       <c r="Q32" t="n">
         <v>593.6709819069124</v>
@@ -37271,7 +37271,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J34" t="n">
-        <v>329.9707069017971</v>
+        <v>324.7905079613318</v>
       </c>
       <c r="K34" t="n">
         <v>105.178570461152</v>
@@ -37316,7 +37316,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y34" t="n">
-        <v>28.35444821007238</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="35">
@@ -37359,16 +37359,16 @@
         <v>220.1374974874373</v>
       </c>
       <c r="M35" t="n">
-        <v>25.26121425459846</v>
+        <v>23.30161829500267</v>
       </c>
       <c r="N35" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="O35" t="n">
         <v>164.7897032902292</v>
       </c>
       <c r="P35" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37435,7 +37435,7 @@
         <v>311.6274301124894</v>
       </c>
       <c r="L36" t="n">
-        <v>436.150196103404</v>
+        <v>433.9385745190985</v>
       </c>
       <c r="M36" t="n">
         <v>276.0650421645042</v>
@@ -37487,13 +37487,13 @@
         <v>57.88619966292134</v>
       </c>
       <c r="C37" t="n">
-        <v>21.70127277818807</v>
+        <v>72.27475335195533</v>
       </c>
       <c r="D37" t="n">
         <v>59.46378194444452</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>64.01909516304346</v>
       </c>
       <c r="F37" t="n">
         <v>70.61714403225807</v>
@@ -37511,7 +37511,7 @@
         <v>353.9707069017971</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>129.178570461152</v>
       </c>
       <c r="L37" t="n">
         <v>14.48250298976183</v>
@@ -37538,22 +37538,22 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>11.39713668587307</v>
       </c>
       <c r="U37" t="n">
-        <v>194.0757398730831</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>118.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>97.55635456989245</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>57.53464715053764</v>
       </c>
     </row>
     <row r="38">
@@ -37590,28 +37590,28 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K38" t="n">
-        <v>235.8016893068637</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L38" t="n">
-        <v>220.1374974874372</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>453.6063548811594</v>
       </c>
       <c r="O38" t="n">
-        <v>562</v>
+        <v>164.7897032902292</v>
       </c>
       <c r="P38" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="Q38" t="n">
-        <v>562</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>6.660440997832051e-11</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -37672,7 +37672,7 @@
         <v>311.6274301124894</v>
       </c>
       <c r="L39" t="n">
-        <v>436.150196103404</v>
+        <v>433.9385745190911</v>
       </c>
       <c r="M39" t="n">
         <v>276.0650421645042</v>
@@ -37721,19 +37721,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>57.88619966292134</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>59.46378194444452</v>
       </c>
       <c r="E40" t="n">
-        <v>64.01909516304346</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>70.61714403225807</v>
       </c>
       <c r="G40" t="n">
         <v>100.581864863388</v>
@@ -37778,10 +37778,10 @@
         <v>137.6490400511193</v>
       </c>
       <c r="U40" t="n">
-        <v>194.0757398730831</v>
+        <v>165.1329468701825</v>
       </c>
       <c r="V40" t="n">
-        <v>37.4705903231423</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
@@ -37790,7 +37790,7 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>57.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -37830,13 +37830,13 @@
         <v>177.4460351758794</v>
       </c>
       <c r="L41" t="n">
-        <v>562</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M41" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="N41" t="n">
-        <v>475.3913777156075</v>
+        <v>561</v>
       </c>
       <c r="O41" t="n">
         <v>164.7897032902292</v>
@@ -37845,7 +37845,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>253.2942842685745</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37915,7 +37915,7 @@
         <v>276.0650421645042</v>
       </c>
       <c r="N42" t="n">
-        <v>328.7468614294096</v>
+        <v>326.5352398451041</v>
       </c>
       <c r="O42" t="n">
         <v>419.0391822801049</v>
@@ -37970,7 +37970,7 @@
         <v>64.01909516304346</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>70.61714403225807</v>
       </c>
       <c r="G43" t="n">
         <v>100.581864863388</v>
@@ -37979,16 +37979,16 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>187.184183724144</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>315.4281634805156</v>
+        <v>353.9707069017971</v>
       </c>
       <c r="K43" t="n">
         <v>129.178570461152</v>
       </c>
       <c r="L43" t="n">
-        <v>14.48250298976183</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -38012,19 +38012,19 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>137.6490400511193</v>
       </c>
       <c r="U43" t="n">
-        <v>194.0757398730831</v>
+        <v>78.57984413493104</v>
       </c>
       <c r="V43" t="n">
-        <v>145.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>118.6271901612903</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>97.55635456989245</v>
       </c>
       <c r="Y43" t="n">
         <v>57.53464715053764</v>
@@ -38061,28 +38061,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>141.7093966296125</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K44" t="n">
         <v>177.4460351758794</v>
       </c>
       <c r="L44" t="n">
-        <v>220.1374974874372</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>253.2942842685745</v>
       </c>
       <c r="O44" t="n">
-        <v>562</v>
+        <v>164.7897032902292</v>
       </c>
       <c r="P44" t="n">
-        <v>562</v>
+        <v>200.3120706125849</v>
       </c>
       <c r="Q44" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38146,7 +38146,7 @@
         <v>311.6274301124894</v>
       </c>
       <c r="L45" t="n">
-        <v>436.150196103404</v>
+        <v>433.9385745190985</v>
       </c>
       <c r="M45" t="n">
         <v>276.0650421645042</v>
@@ -38198,34 +38198,34 @@
         <v>57.88619966292134</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>72.27475335195533</v>
       </c>
       <c r="D46" t="n">
         <v>59.46378194444452</v>
       </c>
       <c r="E46" t="n">
-        <v>64.01909516304346</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>70.61714403225807</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>100.581864863388</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>121.7922509475617</v>
       </c>
       <c r="I46" t="n">
-        <v>187.184183724144</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>8.970706901797143</v>
+        <v>335.2495449521409</v>
       </c>
       <c r="K46" t="n">
-        <v>129.178570461152</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>14.48250298976181</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -38255,7 +38255,7 @@
         <v>194.0757398730831</v>
       </c>
       <c r="V46" t="n">
-        <v>100.1121708998975</v>
+        <v>145.8296897837838</v>
       </c>
       <c r="W46" t="n">
         <v>118.6271901612903</v>
